--- a/ds_cleaned_dataset/discussion_dataset_normalized_cleaned.xlsx
+++ b/ds_cleaned_dataset/discussion_dataset_normalized_cleaned.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion 4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion 5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Discussion 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Discussion 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Discussion 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Discussion 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Discussion 5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,9 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -54,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,11 +65,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -76,6 +85,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,804 +456,791 @@
   </sheetPr>
   <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>I took this course because I had no other choice if I wanted to graduate within eight semesters.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>An idea to analyze the compatibility between new post authors and users by mining 'Twitter(X) Friend Introduction' hashtag data. Customer: primarily myself.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Computer Science senior. Because there are no other options. I believe that pattern mining, classification, and anomaly network detection will be helpful for cybersecurity.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Hidden information in media (news), political bias issues. Unreleased update information for games/TV. I want to find information in my areas of interest through data mining.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>I want to learn properly through a project while taking the data mining course and other computer-related courses together. I chose this course because I want to learn in depth through a data mining project.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Game recommendation system - A system that recommends suitable games without detailed information. It's difficult to find games because there are many, and I want to utilize data mining concepts through game data.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>I hope to study RL, especially AI alignment. I have taken lots of courses in CS and statistics, I haven't done anything. To practice, I'll make the core basis. I'll make bases for AI with data science knowledges and want to complete my own project to improve problem solving skill.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Taking this course to prepare for employment while learning data mining. I want to create things I imagine with data mining.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Life problem. Sleep problem. Irregular sleep due to a bad lifestyle. Possible to improve sleep quality through sleep pattern analysis. I want to address this problem with today's data mining study.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>The reason is that I want to learn about data science. My major is data science, but I didn't learn about data science in university. So, I chose this course and I want to build deeper knowledge about DS.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Data analysis through pattern mining - I am curious how DS is utilized. I want to find patterns in various data and broaden my thinking in the data field.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>This course fits a 3rd-year student who likes games. I have a lot of interest in games and want to analyze game data.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Difficulty using public transportation without KakaoMap updates. Inconvenience due to lack of real-time information. Inconvenience of having to leave 10 times earlier. It would be more convenient if public transportation information was improved through data mining.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>I wanted to get a better understanding of data science. I already took the course for AI. Learned about ML and what to do with data. Good opportunity to learn how and what to do with data to actually solve problems.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>One problem in my daily life is time management. I get distracted (screen time, YouTube, games, history). This class will help me be able to use daily data patterns and knowledge to help me focus better when it is harder.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>I chose to take this class because I am majoring in data science. I also would like to be a data analyst. I once worked in a telecom company and heard that field of data science is one of the most upcoming job positions.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Using raw data to usable data. For example, making a simple yet informative presentation from raw data. Could organize life more by categorizing monthly expenses. Track where money have gone to.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>The main reason is to explore a new path of computer science since I have not yet tried any class related to data science.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Trying to stay on track of my monthly budget. Been 2 years living in Korea University but still overspend. Hope this class helps me manage and recognize data patterns in life.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Using data mining as a system developer living in the AI generation. Studying statistics. I think it can be used in many ways at school as well.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>I want to know how data classification and mining methods are actually used in which systems. I want to understand how feature extraction is performed.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Solving real-life problems through knowledge and tools while learning data mining. I want to study machine learning and AI more deeply and understand how companies actually use them.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Attempting to solve various problems through classification and clustering via data mining. Data mining can be used for providing real-time traffic information or personalized experiences.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Taking the course to improve capabilities when seeking employment. Acquiring background knowledge necessary for taking data mining-related lectures. To build basic knowledge and better understand the class content.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>In the case of classes, there are many results and reaction rates, and it is sometimes difficult to convert data. If handled properly, it can be used in many more cases.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>I chose this Data Science class to improve my analytical and problem-solving skills. Data is an important role in making decisions. I hope this class helps me understand trends and patterns efficiently.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>I have a problem of choosing clothes/shoes to buy. By taking this course, it will help me make better decisions by collecting and analyzing data to see the most bought shoes. Concept of data mining will help choose the best one.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>While reading the book 'Why do machines learn?' during winter break, data clustering content appeared, so I chose it to learn more details at a 4th-year level.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>I want to find patterns related to copyright law in my friend's work. By approaching text patterns using data mining methods, I could solve legal problems.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>I want to solve various problems using data mining and learn by encountering real-world cases.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>It is difficult because there is no way to see a large amount of data at once. I want to find a way to understand difficult-to-see information and organize it at once through data mining.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>To learn more about data mining and how it could benefit website search engine optimization. Planning to integrate data mining insights. Intrigued by how collected and trained data can be extrapolated to predict future or upcoming data.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>An AI model trained with date and specific parameters for a project. E.g. An AI model that collects BMI data and suggests eating habits and exercise based on weight and emotion. Data mining can shorten the research process by half.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>I am a data science student but still don't know what I am learning until now and how to apply it in real world. Had taken machine learning and AI class last semester which could be helpful in this class.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>When people ask me 'what is data science?' I cannot answer. By taking this class and based on the concepts learned, I hope I can answer confidently. I can get out of my own anxiety.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Chose this class for team project. There are lots of advanced LLM models today and also image generation. Hope to learn how these work and make a great data processing class project with team.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Image detection is related to the course concepts. For classification and detection of images, we need high-level pattern matching, data clustering. Real life: cameras on vehicles, CCTVs, autonomous driving (Tesla). Will learn basic concepts and apply to team project.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>I chose this cause because I want to understand how data can be used to solve real world problems. I'm interested in Data Science. This class would help me build a foundation in analyzing data and making meaningful decisions.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>One problem is managing my sleep pattern. By collecting data on sleeping hours, screen time, and daily condition, I can find my sleep quality and build healthier habits.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>I chose this course because I am interested in exploring how data works since every information and knowledge in life can also be considered as data.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Analyze my financial spending habits by looking at my purchases pattern. May optimize for more discounts or reduce overall spending.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Previously studied data mining with a vision-based topic. Want to learn more broadly and in practical fields where data mining can be used.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Game hack detection - detecting cheating in games through data mining by detecting abnormal behavior patterns.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>I want to study in a direction that can be used in graduate school while learning algorithms related to data mining.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>It is expected that personal transportation problems can be solved through data mining.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>I work part-time at a shoe reselling company. Developed a software that mines data to make money.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Edge cases in data, inconsistencies. Also: girlfriend lives near Hanyang and I live at Bomun - many ways to travel from A to B but the best route differs every time. Want to find the consistently best route.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>I actually want to know and understand what data science is. I have a lot of friends in Data Science major but I don't really know what they do or how it differs from CS (AI). Hope this course can give me insights.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>I have many thought processes before I do something. Thoughts are overlapped and cluttered. Maybe I could learn how to process thoughts, know what's redundant, and understand what's important.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Reason for choosing: mostly for fulfilling credits. But it also seemed the most interesting and useful, and we put with data evaluation.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Interesting to analyze reader behavior/patterns. Trying to explain why and how it relates to the world or psychology of a particular kind. Like a sociological/psychological analysis study.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>I'm investigating how software developers improve their methods. Researchers draw out meaningful insights from data. Finding meaningful insights from real world data is important for my research. Chose this course to enhance my research.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>I'm riding subway daily to KU. The subway door closes too early even though there are lots of people to board. If opening door time would be flexibly determined based on data, it would improve subway experience.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>I chose this course to develop my skills to analyze a vast amount of data. Got interested in AI &amp; deep learning. Looking forward to getting knowledge about data science so I can adapt well in AI society where big data is important. Also wanted to experience team project.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>There is too much to study and schedules often conflict. I hope this class will help me coordinate my schedule or organize information by having machines identify patterns.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>I am interested in Data Analysis and it might be considered to be my future career. I wish to learn more concepts, knowledge, and practice in university.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>I do part-time jobs at a convenience store. Customers really buy similar groups of stuff most of the time, which can be categorized by gender, age, Korean/foreigners. That's why Data Science/Data Clustering is interesting.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>One of the interesting topics I would like to know more about. Needed credit hours for major. DS is useful and needed knowledge that may help a lot in future career. Professor's teaching style is interesting.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>This course may help me choose further study field, in terms of company or university/professor. Through classifying and considering all options available, a better choice can be made.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>The course would teach me how to connect dots between other courses (machine learning, regression analysis, data visualization). Will gain better insights of real world data and how it will be processed.</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>I don't read maps very well. When at a shopping mall, instead of looking at store names, I read store numbers in order. Related to data arrangements in information boards where stores can be sorted by category/services alphabetically.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>I want to learn to organize data and know how the field of Data Science is actually applied because data analyst job is trendy nowadays.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>I have problems organizing my belongings in my small house. Need to categorize things I need, throw away seasonal items. The concept of data mining, outlier and detection can be used to solve my problem.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>I was fascinated by the idea that data analysis is like cooking: cleaning and processing raw ingredients to create something meaningful. After learning that 80% of a data scientist's time is spent on data processing, I chose this course.</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>The lack of organization in my Google Cloud storage - massive number of files scattered without clear structure. Want to apply clustering and classification to automatically group similar documents and categorize unsorted files.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>I was interested in methods that can extract interesting knowledge from massive data in various types. Taking this lecture especially to learn modern methods and apply through a team project.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>As a citizen in Gyeonggi province who commutes by public transportation, standing for over an hour is routine. Want to make a new algorithm that provides the best way to sit in train cars using mobile signal density data, adding a 'sitting first' option for route planning.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>I wanted to place all classes in one day.</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Optimizing my nutrition plan by analyzing data on calorie intake, body weight, and exercise performance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>I chose this course to learn guideline of Data Science. I'm afraid of solving problems which don't have specific answers. I want to know some guideline of Data Science (how to define answers, methods).</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>한국어: 글로벌 지표를 공부하며 전문화된 분야에서의 가이드라인을 얻고 싶음.</t>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>While studying global indicators, I want to obtain guidelines in a specialized field.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>This is my first semester after completing military service (discharge date: Feb 26). Was looking for courses to take after returning to school. Found this course and signed up with enthusiasm. First semester back at school after military service.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>As a data science student, I am excited to learn data mining. I believe I will be able to learn the practical applications of data mining.</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>I expect to learn about pattern mining, classification, clustering, and outlier detection, and to be able to identify patterns in people's meditation characteristics by finding them as data through clustering.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>I'm a Data Science major student. I can finally learn more about my major in details. All subjects from previous semesters are kind of broad and general so I still can't see the real definition of Data Science.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>I've always struggled with scheduling and following plans. Can't organize well. Hope this course teaches me how to schedule my daily schedule through Data Mining.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>I would like to start my career as a quantitative researcher at an asset management company. Data mining is highly related to qualitative decisions, so I would like to adopt those types of skills &amp; technologies.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Feature extraction that determines excess returns over the benchmark (factor selection). In other words, avoiding data overfitting (in DL, overfitting).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>I'm interested in AI topics such as machine learning, clustering, etc. Also making statistics to study data analytics. Statistics are highly related to data science. With this course, I can get a lot of help to consider my career.</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>I'm using a company app for shipping and they recommend tools based on my data using clustering in complex ways. I could understand by attending this course how it works.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>My major is data science and still after studying for 2 years, I haven't got a concept of what I'm learning and exactly what my major is. I chose this course to understand truly what I am majoring on.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>I bought an air purifier and I'm curious if I should keep it on 24 hours. The performance and needs would need to match balance with costs. Need data for evaluating and finding an efficient managing way.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>The reason was to get useful insights and skills for my personal data science project. I'm currently researching the relevance between a web novel's certain traits and the novel's hit rate. Data mining, outlier detection, classification would be a great theoretical foundation.</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Researching web novel popularity. Could extract certain traits, filter out irrelevant items, and distinguish safe-to-go needs. Use this class to support my research and predict the hit rate of web novels.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>I want to learn the fundamental concepts of data science as it is detrimental to my major. The team project for this class will help me gain good experience for my future career.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>I tend to get distracted while studying and use my phone a lot. Would be great if I could build something that detects when I am not focused and reminds me to concentrate on my task.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Finished military service at 2026.2.8 and returned to school. School culture, data science, AI, cyber security, machine learning had changed drastically in 2 years. Need to recover and exercise the main concepts and applications.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>I studied cybersecurity and solved hundreds of CTF wargames from Dreamhack. Each paper has basic security theory and problem solving strategy. Some have common features. May I extract or cluster my papers so that I can search my archive efficiently?</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>I want to know more about data science. Also desperately needed to fill the quota for major subject credits. Data science class was a good enough choice.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>I know data science is all about finding interesting patterns. My first 2 years in Korea, my grades were always going lower. But suddenly last semester I got the highest grade. Was it anomalous? Hope I can get a good grade so my grades data will keep increasing.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>I want to understand how data in general works. As a computer science student, I handle data everyday using computers, but not often manually. I decided to take this class to look further in depth.</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>All my friends have different food preferences and allergies which can act as data to decide a restaurant everyone agrees on. Categorizing by dietary restrictions, cuisine preferences, post-restaurant ratings - a recommendation system could suggest suitable restaurants.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Biggest reason: class is on Friday 9AM - needed motivation to wake up after military service (discharged Dec 2025). Second reason: progress of AI - I should train myself in areas AI cannot take over.</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>I'm interested in learning other languages. Since I am a lazy man, I wanted to learn a new language faster and easier. Want to gather many datasets of several methods of learning language to discover the most effective method using MRI pictures, brain waves, behavior, etc.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Data Science is the most important topic nowadays. As a software engineer, I chose to learn core concepts of this lecture to learn what the data says.</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>As a PL enthusiast, I want to devise some role/function language that has some engineers who write clean code for specific language. Want to answer: which tool should I use?</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Because I can solve various problems in the world with data. I became very interested in the introductory machine learning course and wanted to study it further. I wanted to build my ability to handle data.</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>The problem of deliberating on which situation to apply various algorithms to. I would like to practice all the major algorithms through a project, define a real-world problem, and propose a solution.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Reason: I believe when we go to work, wherever we end up will always work with data. Chose this class to improve my data managing skills in preparation for career life. Having extra soft skills is always good for job seeking.</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>I always have problems managing my expenses. Can't manage what to buy and what's not to. I will always end up not knowing where I spent my money.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>It has been one of my bucket list to study and learn about data mining, i.e. how to mine it correctly, the proper method, how to implement novel models. Motivation came from last semester's Deep Learning class.</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>I tend to write lecture notes online using Notion. I do find some connections between my notes despite taking notes on different subjects. Want to apply data mining concepts to clearly organize my notes and relate them based on their relevance.</t>
         </is>
@@ -1258,1016 +1257,954 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The most interesting part I learned today was MCAR/MAR/MNAR. Its concept in broadly missing values chapter. Its base three concepts were a crucial part of my understanding. I had performed a public analysis at several layers of the platform and steps clearly from the start throughout the research process.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Following online resources/libraries in the web panel. When I research the use of libraries, I need patience and author expertise. Finally it was the best practice to get it right.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>The variance method to reduce the dimension of data was interesting. I'm not used to nonlinear reduction methods, but there are still some to try to minimize the difference with minimum variables. I had to study these mathematically.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>It requires more attention when the data has many null or abnormal values. AI agent may create fictitious values for null values, which leads to hallucination. Thus, we need to put more restrictions when prompting. Also even for null or anomalies, we always need to check if the agent made relevant or inappropriate data.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Dimensionality reduction. Because I took the course about regression and multidimensional data, so I'm familiar with dimensionality reduction using linear method but unfamiliar with using non-linear method. Through today's class I learned about dimensionality reduction. In reason it is the most interesting thing.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>In my experience AI agent didn't understand correctly about data types and formats, so AI agent was wrong about data preprocessing. Thus we should know the intermediary about data before using AI. The agent would be cautious about its worth if AI shows proper result.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Learned about KL divergence, visualization, similarity measures. Found it interesting how different visualization methods can reveal patterns in data. Discussed AI agent capabilities for data analysis.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Need to be careful when using AI agents for data processing. The agent might misunderstand the context of the data. Need to verify the results carefully and understand the limitations of the tools.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Learned about MCAR, MAR, MNAR concepts and how they affect data analysis. Found it interesting that different types of missing data require different handling approaches.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>When using AI agents for data preprocessing, need to be careful about how the agent handles missing values and outliers. The agent might not understand the domain context properly.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>The preprocessing step was the most interesting thing I learned. I love how it tells a story about how data was collected and uncovering patterns. That is more like detective work than data processing. This is why the preprocessing was the most interesting thing during the class.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>We always have to be careful when we use AI agent for data understanding and preprocessing because of hallucination and its inability to fully comprehend the data context. Need extra attention when using AI for data preprocessing.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Found visualization and independence analysis interesting. Learned about how to use different plots and charts to understand data distributions and relationships between variables.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>When using AI, need to verify the outputs. The AI might generate plausible but incorrect visualizations or analyses. Need to understand the data before asking AI to process it.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>The most interesting thing is PCA. I found PCA moves the dimensionality, and it can be done by general case and unprincipled capturing of the data. It also expands to visualize at a specific format. It was interesting.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>I would say when there are many null values and the data has a lot of noise. These recommendations may not be accurate since the AI may suggest things that don't make sense for the specific context.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Sources of potential problems: Errors and noise, Incompleteness, segments, missing entity, duplicate, fictitious, conflicto. Lack of semantics, unlabeled, bad quality, data integration and attributes. When we look at data paths, our integration and environment is the data source.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>I care about an AI agent for data understanding and preprocessing for the purpose of making and preparing data models. Many misinterpret data common errors or in noise data. Flavoring in conversational-models, a biased data can lead to inconsistent results.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Learned about different data types and preprocessing methods. Found it interesting how different visualization techniques can help understand data better.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Need to be careful about data quality when using AI. The AI might not detect subtle errors in the data that a human expert would catch.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Learned about LLM and how AI processes data. Found it interesting that AI can assist in data visualization and analysis, but it requires proper understanding of the underlying data.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>When using AI, the preprocessing step is crucial. Need to ensure data quality before feeding to AI. The output quality depends on input data quality.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Data preprocessing and visualization were the most interesting topics. Understanding how to clean and prepare data is fundamental for any analysis.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>When using AI for data tasks, need to verify the preprocessing steps. AI might apply inappropriate transformations that could distort the analysis results.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Data cleaning is the most interesting part because it's the step that requires judgment, not just technique. You have to decide why the data is messy before you can fix it. Every dirty dataset tells a story about how it was collected and uncovering that is more like detective work than data processing.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Data leakage: agents can accidentally use future information to preprocess past data, which silently inflates model performance. Label encoding decisions, when encoding categorical variables, an agent might impose an arbitrary ordinal ranking where none should exist, introducing false structure.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>What I found interesting is that the importance of data can be measured by different aspects. For example, effects like missing values, duplicated types like noise, sampling approaches - all of these are different measures that represent different dimensions of the data quality.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Data can be stored in very different types. It can also have extreme values. AI agents could be used for this, but the results may vary. Some data types may be recorded and treated differently by different tools. Ensure data consistency.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Today I learned that I learned today is that we can extract data in different subjects, but some data can be complex for a short description. The data is related with so many concepts. We need to check if the data meets requirements after preprocessing.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Data objective is that AI agent and data understanding means data preprocessing and integration, which requires more investigation. Also data handling for understanding may not always be straightforward. It requires domain knowledge.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Learned about data types and how different representations of data affect analysis. Found it interesting that preprocessing choices can significantly impact results.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>AI agents need to understand the context of the data. Without proper context, the preprocessing steps might be wrong or misleading.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>I think the most interesting thing is visualization. It was interesting and it helps us to understand data better. There are various types of visualization tools that we can use to analyze data.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>I think the data pre-processing step should be treated with more attention. There are some cases when the models can be biased or have wrong results if we miss cleaning step.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Before this, I only learned the importance behind it, and its preprocessing. But very I thought it was more like a routine I had to do. But I was surprised that there was a lot of method to it. I learn more about MCAR, and MNAR and if there was a pattern to it. I found it very interesting, I learnt today.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Extra attention when using AI agents: I think we have to pay agents to make decisions. Use data understanding the data first, then fill in data with the data understanding. Needs management while AI agents, we also need to pay attention to the data's privacy and fix it to be looked.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Learned about different methods of handling missing data. The concept of using statistical methods to handle missing values was the most interesting part of today's lecture.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>When using AI agents, need to pay attention to the data format and structure. AI might not handle certain data types correctly without proper preprocessing.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>The most interesting thing is about data preprocessing. It's important to understand why data cleaning and preprocessing matter before analysis. The concept of data quality dimensions was enlightening.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>When using AI for data tasks, need to understand the limitations. AI agents may not always correctly identify outliers or handle missing values appropriately without human guidance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>What I found most interesting today was that the different concepts of data can be measured. The different dimensions like completeness, accuracy, for instance, like man and woman, king and queen, make the same distance with each other. I never thought of it that way because I never thought of it.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Maybe when we have special or uncommon data. How could this change the result significantly from approaches with caution.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>I found it was a very kind helpful process and I've learned various topics in today's lecture. The most useful was data preprocessing. It helped me organize and I want to better understand the subject of AI and data science. It also made me understand more about data.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>In detail, I found some interesting things. It also provides help in an example to use a model for each analysis. It would probably be related to learning topics and be changed to get results. I think it was more interesting in all aspects.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>I think the most interesting thing that I learned today is that easy type of data and for different approaches, reasons and the data before. I saw familiar concepts like before, with the update and transformation of data types in today's class and I think it is very useful for studying.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>I think it is very important to check data cleaning, and maybe the AI agent might generate wrong data. Some data that are recently created might be wrong in data processing, tables and data might turn out to be different.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>I got to know about how to handle with data, there is so much. Categories and a lot of examples to understand. Even more, I would learn more from it. Knowledge is consuming. It in my area, it is good to know in short time. It will need to learn to have that ability.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>A guess that what we're collecting makes the data sources one type. To look information to internet. Therefore its important to know the sources. We should be and data should be discriminate and according to be interesting.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>The most interesting thing that I learned today is about data preprocessing and why it is important step for the next data analyzing. It requires knowledge and techniques. I think it is well interesting because it seems like it takes a lot of practice to do well in this step. The concepts such as data cleaning dealing with missing data, visualizations are crucial knowledge.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>One of the cases where I might need extra attention when using an AI agent for data understanding and preprocessing is the purpose of analysis task. In my opinion, the subject of analysis is important. For example, a doctor might wish to find outlier in patient's medical report to detect any health problem. At the same time, hospital/government might wish to find the average health conditions.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>About how the molecular and the reduction, the most interesting thing I learned was about independent analysis concepts. Found it interesting about how the overall concepts work.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>AI agents can have errors and when we handle data, there might be issues. Need to understand the context of data. The UMAC and other concepts were useful.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>I think today's class was about the confusion and class related to data cleaning. Some data are not easy to find. I used to think the data is already clean but I found it was not the way. It is important to learn in this step.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>I think data should be always understanding the data. If pre-processing is not correct, some analysis and the metrics will be wrong. We need to check the data before analysis.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>What I learned today is about visualization and data types. When I was looking at the types of data, their visualization. I also have different grades and graphs can capture different objects. I also enjoyed learning how different data objects can be related. How to point an equation with variables or logical thinking.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Extra attention. Recently I will not only explain whether the data can be very powerful. To true opinion in testing. AI agent can in terms of everything and establishing thing like hypothesis inference or observation. The data pattern has or incorrect. Additional attention may be given to gain understanding. Please additional questions may be given if neglected.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
         <is>
           <t>I say that our data visualization abilities. It is also useful and very important to data. It is useful. AI and therefore AI helped me in knowing my understanding in the subject of AI and data science, it also useful and helpful. I say I think our data community is also important. Thus we are able to be processed or advanced. Our data evolves each time and we can get a result possible by AI. These agents enable analysis to be done when it is needed.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Learned about data types and formats. Found it interesting how different representations affect the analysis approach.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>When processing data, need to verify the output format. AI may change formats unexpectedly. Need proper validation steps.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>It was interesting that noisy data can be helpful for avoiding overfitting.</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>When we use AI agent, it is important that data tells different agent. For example, data value 'null' can be interpreted in various meanings.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Data preprocessing and visualization were most interesting. Learning about different types of missing data and how to handle them was valuable.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>AI agents need proper instructions for data handling. Need to specify the exact preprocessing steps wanted, otherwise the agent might make wrong assumptions.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>The most interesting thing I learned today is the different types of missing data (MCAR, MAR, MNAR) and how each requires a different approach for handling. This is important because it directly affects the reliability of the analysis.</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>When using AI agent for data understanding and preprocessing, we need to be careful about domain-specific issues. For example, in medical data, missing values might have clinical significance. The agent might fill in values that are statistically reasonable but clinically inappropriate.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>The most interesting thing I learned today is that LLM model will preprocess data. We are able to understand that the data preprocessing step has its importance. But also I think that we have to see both supporting data without this step. The better data, the better result. The preprocessing step is important but it really only is the understanding. But it holds no value.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>For me the most interesting thing we learn today is visualization of data is interesting, as it make a long or complex or direct data easily understood by representing it using plot, graph or any visual. It is a phrase that 'one picture is worth a thousand words'. And it also the least complex they've learn today.</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>In my opinion, I think that need extra attention. It is a case when the data have extreme values. The AI agent then even follows pattern. extreme value may seem irrelevant but it don't need the pattern, maybe AI will learn it as an error and ignore the pattern. If the data of customer buying order normally 0~200 dollar, and suddenly there is 16,000 dollar, that is an error that we should know.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>What's interesting: I'm amazed at how data can be represented into discrete and continuous. Also data can be represented as regression or categorization. The possible different ways of learning is interesting.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Error detection: All special things split from know and it, I heard of many how plus and group to all. It means from 2 and take what can be integrated as real data. Solely goal data can be complicated. So who using data from AI too complicated words, we need to think about the data truthfully on the data before using it.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Society. The people relation the modeling and also when data comes and only the learning that the data it to its more. I am expected to like the way in like itself.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Data types differences. Understanding data types is visualizing my learning. Since data are at several involved has diagram new, think &amp; use graph &gt; understanding everything.</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>People Hackathon: a labeled but great data attention is needed. It requires them smaller results/labels making mistakes. Every types list of data. In setting patterns and some reading. Mining update + contribution. Monitoring makes new errors. Since the data update, since off or model mistakes, double-check needs to be accurate or multiple inputs to be done by human or multiple inputs.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Importance of preprocessing in the data. When data is stored and it shows while it seems important, then it the data of AI, LLM, and only state models. If data was reformated the resulting model will change. If this sense more important than the model or computing methods.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>In some cases, we need to know the result (true or false) they are the exceptions/outliers (this is the reason why we learned about errors, and they). Therefore making the AI open to values for outliers. Where data should be handled with basic shape. Hence we handle these.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="A41" t="n">
+        <v>41</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>There is two very interesting things for today. The first one being there are various types of visualization. We can show all of them by using plots, charts and graphs. I want to use in my field. I see some having fun tables to turn to so we see visualization and data visualization about the question of AI generate plot to analyze chart in the real life.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Extra attention when using AI agent. I think nowadays do really great work. For me personally they can do many work even more. So even AI can do it, trusting AI work is not good. So we need to double check it! It is fabricating or generating some data about on this. This double checking process is especially important when it comes to sensitive data add-on.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>There is two very interesting things for today. The first one being there are various types of visualization. We can show all of them by using plots, charts and graphs. I want to use in my field. I see some having fun tables to turn to so we see visualization and data visualization about the question of AI generate plot to analyze chart in the real life.</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Extra attention when using AI agent. I think nowadays do really great work. For me personally they can do many work even more. So even AI can do it, trusting AI work is not good. So we need to double check it! It is fabricating or generating some data about on this. This double checking process is especially important when it comes to sensitive data add-on.</t>
+      <c r="A42" t="n">
+        <v>42</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A data 100 visualization site was interesting.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AI tends to use 'the most popular method' unless clarified otherwise. If not directly asked, AI might fill in invalid (N/A) data with average value when it actually needs to be deleted or filled with 'unknown', or vice versa.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>A data 100 visualization site was interesting.</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>AI tends to use 'the most popular method' unless clarified otherwise. If not directly asked, AI might fill in invalid (N/A) data with average value when it actually needs to be deleted or filled with 'unknown', or vice versa.</t>
+      <c r="A43" t="n">
+        <v>43</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Data Analysis, and today I found weight analysis working. Without expert review. Weight case analysis is important. But today professor told us data analysis in movie weights. The movie derived in movie analysis weights case in real world. The picture describing in movie weights. LLM makes we look forward to assigning the feature at data science.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>When working on an AI agent for data is getting smarter and can perform various functions. However, I think it is important to decide methods and how to use LLM in specific domains. Not using an AI agent for all fields, we have to think creatively and can explain why and how to use LLM.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Data Analysis, and today I found weight analysis working. Without expert review. Weight case analysis is important. But today professor told us data analysis in movie weights. The movie derived in movie analysis weights case in real world. The picture describing in movie weights. LLM makes we look forward to assigning the feature at data science.</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>When working on an AI agent for data is getting smarter and can perform various functions. However, I think it is important to decide methods and how to use LLM in specific domains. Not using an AI agent for all fields, we have to think creatively and can explain why and how to use LLM.</t>
+      <c r="A44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Learned about data visualization and preprocessing. Found it interesting how visual representations can reveal hidden patterns in data.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AI agents should be used carefully for preprocessing. Need to validate results and understand the domain context before applying AI-generated preprocessing steps.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Learned about data visualization and preprocessing. Found it interesting how visual representations can reveal hidden patterns in data.</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>AI agents should be used carefully for preprocessing. Need to validate results and understand the domain context before applying AI-generated preprocessing steps.</t>
+      <c r="A45" t="n">
+        <v>45</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>The most interesting thing I learned today has to do with data science. I realized that data science has a lot to do with attribute relationships. Two datasets with categories and attributes should be well covered in PCA. These are all closely related. I was able to see clearly my research including finding a very close relationship with my research.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>I also want to ask about when using AI agent data understanding or preprocessing for data. If I put sensitive or subjective data to AI agent, the data might be passed to paper AI experts somewhere. Positive or negative experience that I've tried to summarize the paper of GEMME, so I should do critical thinking on the summary, the AI agent remained.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing I learned today has to do with data science. I realized that data science has a lot to do with attribute relationships. Two datasets with categories and attributes should be well covered in PCA. These are all closely related. I was able to see clearly my research including finding a very close relationship with my research.</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>I also want to ask about when using AI agent data understanding or preprocessing for data. If I put sensitive or subjective data to AI agent, the data might be passed to paper AI experts somewhere. Positive or negative experience that I've tried to summarize the paper of GEMME, so I should do critical thinking on the summary, the AI agent remained.</t>
+      <c r="A46" t="n">
+        <v>46</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The most interesting thing is that it happened this year and how new AI does. I received a visual model that removes every related data. It is related about it being together. The reasoning is the most important idea. It is related.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>I would pay when AI is able to perform tasks like finding the patterns. I said of finding the related ones. The reason is because the AI agent cannot attend to do my analysis. For example, in the case at a situation, Rashikid used AI and it ended up citing a case wrongly and even creating a case that never existed.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing is that it happened this year and how new AI does. I received a visual model that removes every related data. It is related about it being together. The reasoning is the most important idea. It is related.</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>I would pay when AI is able to perform tasks like finding the patterns. I said of finding the related ones. The reason is because the AI agent cannot attend to do my analysis. For example, in the case at a situation, Rashikid used AI and it ended up citing a case wrongly and even creating a case that never existed.</t>
+      <c r="A47" t="n">
+        <v>47</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>About data types and visualization concepts. Learned about different ways to process and handle data. Found the various data handling techniques interesting.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>When using AI, especially for data tasks, need to be mindful of the context. The AI might not have enough domain knowledge to make proper decisions about data preprocessing.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>About data types and visualization concepts. Learned about different ways to process and handle data. Found the various data handling techniques interesting.</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>When using AI, especially for data tasks, need to be mindful of the context. The AI might not have enough domain knowledge to make proper decisions about data preprocessing.</t>
+      <c r="A48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Found the classification and dimensionality reduction concepts most interesting. Learning about how data can be transformed for better analysis.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AI agents need careful monitoring when preprocessing data. The automated processes might introduce errors that are hard to detect later.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Found the classification and dimensionality reduction concepts most interesting. Learning about how data can be transformed for better analysis.</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>AI agents need careful monitoring when preprocessing data. The automated processes might introduce errors that are hard to detect later.</t>
+      <c r="A49" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>I just interesting thing is that today I learned that data cleaning and preprocessing are really important. What I really important in data analysis. I think data preprocessing is the key to getting good results from any analysis. Without clean data, the results will be unreliable.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>When working with AI agents for data tasks, we need to be especially careful about data privacy and security. Also, AI might make assumptions about the data that are incorrect, leading to wrong preprocessing decisions. Human oversight is essential.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>I just interesting thing is that today I learned that data cleaning and preprocessing are really important. What I really important in data analysis. I think data preprocessing is the key to getting good results from any analysis. Without clean data, the results will be unreliable.</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>When working with AI agents for data tasks, we need to be especially careful about data privacy and security. Also, AI might make assumptions about the data that are incorrect, leading to wrong preprocessing decisions. Human oversight is essential.</t>
+      <c r="A50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The most interesting thing I learned today is about data understanding and preprocessing. I could see that understanding patterns and relationships in data is very important. Data visualization helps a lot in understanding complex datasets. I also found the concept of missing value handling very important.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Base case where I need extra attention when using AI agent. By data understanding and preprocessing. Smart or no problems there: as AI agent may be making mistakes(error). Observing the data going the step the AI agent should be helpful, but how for example, this AI may be sometimes data understanding helps meaning analysis. However, it want or require an extreme instance or situation. Data label by itself - need have Positive/True/False that this time concluded in Validated by very help, and to try or remove may know reducing.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing I learned today is about data understanding and preprocessing. I could see that understanding patterns and relationships in data is very important. Data visualization helps a lot in understanding complex datasets. I also found the concept of missing value handling very important.</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Base case where I need extra attention when using AI agent. By data understanding and preprocessing. Smart or no problems there: as AI agent may be making mistakes(error). Observing the data going the step the AI agent should be helpful, but how for example, this AI may be sometimes data understanding helps meaning analysis. However, it want or require an extreme instance or situation. Data label by itself - need have Positive/True/False that this time concluded in Validated by very help, and to try or remove may know reducing.</t>
+      <c r="A51" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The most interesting thing I learned today is knowing the inaccuracy of data when it comes to the data itself. There was a missing data that is left behind. It means we need to learn how to see left over. However, after learning the deep reasoning behind it, which are called missing data. I learn of traits that are surprising that at some point in reality it was clean if it actually surprising to be the first.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>In the case where we need to give attention for data understanding when AI agent, we need to check on calculations and prescription. Filling this information for it. Create data types. For example, average/median/after data. Even though the average load what median. Smart is. We need to have data. Next, it we need that data. The AI agent has to give extra attention. If we use tables, instructions/situations, etc. But they cannot problem. We need extra effort and attention to understand the data to. We can actually explain to others and sometimes we can spot something wrong generated by the AI agent if we fully understand the data meaningfully and thoroughly.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing I learned today is knowing the inaccuracy of data when it comes to the data itself. There was a missing data that is left behind. It means we need to learn how to see left over. However, after learning the deep reasoning behind it, which are called missing data. I learn of traits that are surprising that at some point in reality it was clean if it actually surprising to be the first.</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>In the case where we need to give attention for data understanding when AI agent, we need to check on calculations and prescription. Filling this information for it. Create data types. For example, average/median/after data. Even though the average load what median. Smart is. We need to have data. Next, it we need that data. The AI agent has to give extra attention. If we use tables, instructions/situations, etc. But they cannot problem. We need extra effort and attention to understand the data to. We can actually explain to others and sometimes we can spot something wrong generated by the AI agent if we fully understand the data meaningfully and thoroughly.</t>
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Thought in is relatively important: deep representation learning. Set in very intrigued in how neural networks work. Also how bits work is providing the world today more complex algorithms larger transformation of preprocessing. Basically it is simple logic. But we need to understand the basis of AI. It is believed we need to understand everything before we use AI for data. Gather analysis / processing a system-level / properties we can that the proper matter a lot even when using an AI agent. Teachers instead of wasting for its better to prompt and try one.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Also the people matter a lot even when using an AI agent. Teachers instead of wasting for a conclusion. Its better to prompt and try one by one.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Thought in is relatively important: deep representation learning. Set in very intrigued in how neural networks work. Also how bits work is providing the world today more complex algorithms larger transformation of preprocessing. Basically it is simple logic. But we need to understand the basis of AI. It is believed we need to understand everything before we use AI for data. Gather analysis / processing a system-level / properties we can that the proper matter a lot even when using an AI agent. Teachers instead of wasting for its better to prompt and try one.</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Also the people matter a lot even when using an AI agent. Teachers instead of wasting for a conclusion. Its better to prompt and try one by one.</t>
+      <c r="A53" t="n">
+        <v>53</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>The most interesting thing that I learned today is about the similarity. The reason is because the similarity that need to be measure. When we are facing a data, there can be very alternate ideas. It's like the the meaning is important. Especially when facing data, contain very alternate types.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>I think only the extra attention is AI agent. As we say that we need to vary, large dataset. Apart from that, so that the AI agent the data properly, rather than one AI purpose only, but not best. Whether the result is good or better. Performance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing that I learned today is about the similarity. The reason is because the similarity that need to be measure. When we are facing a data, there can be very alternate ideas. It's like the the meaning is important. Especially when facing data, contain very alternate types.</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>I think only the extra attention is AI agent. As we say that we need to vary, large dataset. Apart from that, so that the AI agent the data properly, rather than one AI purpose only, but not best. Whether the result is good or better. Performance.</t>
+      <c r="A54" t="n">
+        <v>54</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Most interesting thing I learned is NO, meeting of data preprocessing in data science letter building any model, data will be cleaned and inputed. Raw world data can be going complicated to collected the data, and more going to understand about them. Then we can make it more. Could also visualize into graph to make it more passthrough and easier for all. Development.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Data attention is included when AI agent handle missing value, fill missing value, it would automatically fill values or reduce, although this is use. The proper analysis, some point even. Data AI agent used it in the data value that might not be exact. Could be measure of a different meaning, units or meanings. Holding that data AI agent for data processing. Human is still necessary when using AI agent for data preprocessing.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Most interesting thing I learned is NO, meeting of data preprocessing in data science letter building any model, data will be cleaned and inputed. Raw world data can be going complicated to collected the data, and more going to understand about them. Then we can make it more. Could also visualize into graph to make it more passthrough and easier for all. Development.</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Data attention is included when AI agent handle missing value, fill missing value, it would automatically fill values or reduce, although this is use. The proper analysis, some point even. Data AI agent used it in the data value that might not be exact. Could be measure of a different meaning, units or meanings. Holding that data AI agent for data processing. Human is still necessary when using AI agent for data preprocessing.</t>
+      <c r="A55" t="n">
+        <v>55</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The most interesting thing I learned today was this year about problems in data such as missing or noisy/incomplete values. I found this especially interesting because it showed how data preprocessing affects the quality of analysis and how important it is to set a proper cleaning step.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>I had some examples to make the AI agent realize why data is important/necessary. The first role. When data is displayed values the agent may still correctly. Preprocessing-deleting others' data understanding the context. It still requires an AI agent in preprocessing. Human reading is still important.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing I learned today was this year about problems in data such as missing or noisy/incomplete values. I found this especially interesting because it showed how data preprocessing affects the quality of analysis and how important it is to set a proper cleaning step.</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>I had some examples to make the AI agent realize why data is important/necessary. The first role. When data is displayed values the agent may still correctly. Preprocessing-deleting others' data understanding the context. It still requires an AI agent in preprocessing. Human reading is still important.</t>
+      <c r="A56" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>We can visualize data through many tools, not specifically through scatter plot method. I found it interesting to use it for finding pattern and relations between data mathematically.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>When using AI agent for data understanding and preprocessing, we need to be aware of data accuracy produced by the agent, since it can lack important context and details. Also would it be able to recognize bias/filled or missy values.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>We can visualize data through many tools, not specifically through scatter plot method. I found it interesting to use it for finding pattern and relations between data mathematically.</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>When using AI agent for data understanding and preprocessing, we need to be aware of data accuracy produced by the agent, since it can lack important context and details. Also would it be able to recognize bias/filled or missy values.</t>
+      <c r="A57" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>The most interesting thing I learned today is the collecting and discovering data concepts and how our subject familiar or rather how to demonstrate the data and the concepts I think. It's important to know and also everything and will reasoning well and most part.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>I think we could even attach new ones like target to think an explosion level in volume that is to our control. Both with other data. Together, is to establish normally and understand. Verify the consideration with the related behind.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing I learned today is the collecting and discovering data concepts and how our subject familiar or rather how to demonstrate the data and the concepts I think. It's important to know and also everything and will reasoning well and most part.</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>I think we could even attach new ones like target to think an explosion level in volume that is to our control. Both with other data. Together, is to establish normally and understand. Verify the consideration with the related behind.</t>
+      <c r="A58" t="n">
+        <v>59</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>I think interesting things. It was about visualization and data types. When I was looking at the types of data visualization, I also enjoyed to be how different data and graphs can capture insights and be presented in a meaningful way.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Extra attention. I will try to see evaluating on how to it easy relation. All real test not evaluating whether the description given is true from or not working. AI agent can be very powerful. In terms of everything and establishing thing like hypotheses. Inference or observations. Observing the data pattern has or incorrect. Additional attention must be given to gain understanding. Place and other questions may be given if neglected.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="A59" t="n">
+        <v>61</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>The most interesting thing I learned. A lot of compelling processes when it comes to data, the most useful I found is the preprocessing data. The initial step at data analysis the pair. And I think the properly step with certain method to combine and together it all in many related to explore the scope that represents a different data.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The case related. We are very understanding that data especially in the preprocessing should be in a very hands on understanding. Care as LLMs are currently good but understanding the data own better and bias. So it might just submit the data analysis just to satisfy the user. It should be a more filled data analysis. I believe the understanding of validated results. Its my data interpretation should not be interpreted by AI. It is hoped better understanding. Information on it should be focused in understanding.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>I think interesting things. It was about visualization and data types. When I was looking at the types of data visualization, I also enjoyed to be how different data and graphs can capture insights and be presented in a meaningful way.</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Extra attention. I will try to see evaluating on how to it easy relation. All real test not evaluating whether the description given is true from or not working. AI agent can be very powerful. In terms of everything and establishing thing like hypotheses. Inference or observations. Observing the data pattern has or incorrect. Additional attention must be given to gain understanding. Place and other questions may be given if neglected.</t>
+      <c r="A60" t="n">
+        <v>62</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Patterns finding was initially a similarity of data and its preprocessing. I found it was fascinating that you can look at the patterns and compare it mathematically by looking at the same development, and it was interesting to see how it can be established, relationships between kinds of objects.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AI must be able to correctly check all the data entries' format since all models don't extract perfectly, and that could lead to the reason why the receiving generated results. Also they would lead and what we wanted. Also at the beginning of the agent, it's better understanding of how this works will help produce better results.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="A61" t="n">
+        <v>63</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Found dimensionality reduction and PCA concepts most interesting. The mathematical basis behind these techniques was enlightening.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>When using AI for data tasks, the agent might oversimplify complex relationships in data. Need domain expertise to guide the AI properly.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing I learned. A lot of compelling processes when it comes to data, the most useful I found is the preprocessing data. The initial step at data analysis the pair. And I think the properly step with certain method to combine and together it all in many related to explore the scope that represents a different data.</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>The case related. We are very understanding that data especially in the preprocessing should be in a very hands on understanding. Care as LLMs are currently good but understanding the data own better and bias. So it might just submit the data analysis just to satisfy the user. It should be a more filled data analysis. I believe the understanding of validated results. Its my data interpretation should not be interpreted by AI. It is hoped better understanding. Information on it should be focused in understanding.</t>
+      <c r="A62" t="n">
+        <v>64</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>The most interesting thing that I learned today is similarity. Altough I used to only Semantic/sim, but I know most similarity in the same method. However, things I find it also in measuring things. Similarity can help us to capture the whole meaning. It is interest computing by some codes. Helps it word.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AI not our own knowledge (with technology) can work the models of AI. It can be measured in different way of make any mistake. It at that contribute it out keep this model. However, as it is understanding, this can cause more problems because important of it. In system, dimension can be deleted by the environment. AI pixel that know event then becomes. And I think we should care more it. Are its about specific diversity. Should be copied when we impress the data.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Patterns finding was initially a similarity of data and its preprocessing. I found it was fascinating that you can look at the patterns and compare it mathematically by looking at the same development, and it was interesting to see how it can be established, relationships between kinds of objects.</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>AI must be able to correctly check all the data entries' format since all models don't extract perfectly, and that could lead to the reason why the receiving generated results. Also they would lead and what we wanted. Also at the beginning of the agent, it's better understanding of how this works will help produce better results.</t>
+      <c r="A63" t="n">
+        <v>65</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Learned about data types, visualization methods, and preprocessing techniques. The practical applications of these concepts were the most interesting.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AI agents need human supervision for data tasks. Without proper oversight, the preprocessing steps might introduce biases or errors.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Found dimensionality reduction and PCA concepts most interesting. The mathematical basis behind these techniques was enlightening.</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>When using AI for data tasks, the agent might oversimplify complex relationships in data. Need domain expertise to guide the AI properly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>The most interesting thing that I learned today is similarity. Altough I used to only Semantic/sim, but I know most similarity in the same method. However, things I find it also in measuring things. Similarity can help us to capture the whole meaning. It is interest computing by some codes. Helps it word.</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>AI not our own knowledge (with technology) can work the models of AI. It can be measured in different way of make any mistake. It at that contribute it out keep this model. However, as it is understanding, this can cause more problems because important of it. In system, dimension can be deleted by the environment. AI pixel that know event then becomes. And I think we should care more it. Are its about specific diversity. Should be copied when we impress the data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Learned about data types, visualization methods, and preprocessing techniques. The practical applications of these concepts were the most interesting.</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>AI agents need human supervision for data tasks. Without proper oversight, the preprocessing steps might introduce biases or errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A64" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Understanding data visualization and classification concepts was most interesting. Found it valuable to learn about different approaches to data preprocessing.</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>When using AI agents, need to verify all preprocessing steps. The agent might not handle edge cases properly, and human review is essential for ensuring data quality.</t>
         </is>
@@ -2284,58 +2221,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q1 (Think about a real-world scenario where pattern mining can be applied to. What is a possible example of a transaction, an itemset, a frequent itemset and an association rule?
-</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Q2 (What can be other criteria (In addition to support &amp; confidence) to find "interesting pattern"?</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>example translation is Query keyword on the Internet browser. Request itemset are the related suggested searches. For example, python tutorial, pandas dataframe (coding).
 Association rule is python tutorial -&gt; pandas, python -&gt; dataframe when seen in many platform. Therefore, the interest expire suggest 'dataframe' when we search for 'python tutorial'!</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>We can use LIFT criteria.
 LIFT solves by mitigating the correlation between being random and being an actual pattern by include both the union of the two variables S(A U B) and probability of the two variables S(A) x S(B).</t>
@@ -2343,16 +2266,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">
 - Combining the data set of people purchasing things in a shop and data set of different kinds of shop. For instance, a family may have a tendency to buy some new stationeries for their children during school semester start at a stationery shop. However, the same family may also have a tendency to buy new clothes, or shoes with the same reason. The concept is the same but it's applied on another level above the data set. This scenario can be applied on shopping mall, book festival, or even ad suggestion @ online retailer layout.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">
 - seasonal events
@@ -2363,126 +2286,81 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Many web-novel platforms like 'Kakao page' or 'RIDI' label their novels by keyword (tag).
 In this case, an individual novel's ID and its keyword set can be considered as TID and itemset from the Market basket analysis in today's class.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>According to my personal experience, 'Independence' was a valuable criteria. For example, in the web novel market, there are genres like 'Modern Fantasy' or 'Romantic Fantasy'. They are hybrid genres. So the question arises that "Is Modern Fantasy the same with 'Modern' and 'Fantasy'?"</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>natural language processing. Every conversation can be considered as a transaction. Every combination of words can be considered as an itemset. and the frequent sets of words are the frequent itemset. and the relation between words can be considered as an association rule. For instance, we can investigate about the frequent words used and their relationships, and we can compare if there is a difference between nations. For example, Koreans uses words such as '아이', '근데', frequently, and also combines them as '아이근데', maybe there could be some relationships and one could have a influence on another.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>- One criteria is to investigate the start and end. If there is a sequence. By including those condition, we can know more information than just knowing the support by counting everything. By applying this method, we can change the scope of the investigation and can get more interesting patterns.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>The log of game item purchasement.
 ^transaction
 For example, a lot of companies make some item combinations cheaper when users buy items separately. itemset This is because companies know users make purchase those items together</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>we can use an outlier. I think when specific patterns appears it would show us unusual data. So, if we discover some outlier it can tell us some rules or patterns</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">
 In course enrollment system, the records of all the courses that student in a specific department enrolled. We can consider [department, grade, course1, course2, …] as a transaction. Then frequent itemsets could be like, {Data Science, Algorithm, Computer Programming}, {Freshman, Academic English, Statistics}, ... etc.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve"> we can group the items and observe the relationships between groups of within group.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="9">
+      <c r="A9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t xml:space="preserve">
 In game industry, pattern mining can be used to detect bot (autopilot) detection. A company can collect player's action data. In this dataset, bots will show abnormal action patterns.
 Train the model with previous bot examples, and detect suspicious players.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">
 We don't have to focus on common/main patterns. Sometimes we have to find rare patterns (which can be critical)
@@ -2490,26 +2368,26 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="10">
+      <c r="A10" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>In supermarket, a transaction can be a customer's purchase containing items like bread, milk, juice, and eggs. An itemset is a group of items bought together, such as {milk, bread}. An frequent itemset is one that often appears across many transactions, for example {milk, eggs}. An association rule could be: if customers buy {milk, eggs}, they are likely to buy eggs as well.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Another useful criterion in "confidence improvement" which measures how much the confidence of a rule increase compared to related simpler rules. It helps identify whether adding more items to a rule actually provides new and meaningful information rather than redundant patterns.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="11">
+      <c r="A11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Can be applied in discerning what courses students frequently register for during course registration in order to know the demand and what courses are usually taken in the same semester.
@@ -2524,18 +2402,18 @@
 Association rule: Taking DS may lead to taking DB</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Lift to see if two courses are independent or are entirely correlated.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="12">
+      <c r="A12" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>A single customer's purchase during one visit to the online store. For example, Transaction 1: {Laptop, Mouse, USB drive}.
 Itemset:
@@ -2546,33 +2424,18 @@
 A rule derived from frequent itemsets, such as {Laptop} → {Mouse}, meaning customers who buy a laptop also tend to buy a mouse.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Conviction: measures the degree of implication of the rule (how dependent the occurrence of Y is on X.
 Novelty: indicates how new or unexpected the pattern is.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="13">
+      <c r="A13" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">
 ↳ Maybe E-Commerce can apply this way.
@@ -2580,7 +2443,7 @@
 •</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">
 ↳ Shifting our perspective, How about considering the probability of Y not occurring given that X has occurred.
@@ -2588,28 +2451,28 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+    <row r="14">
+      <c r="A14" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t xml:space="preserve">
 A. Years and movies. Frequent itemsets can be commonly seen popular movies. Association rules can be that movie genres other user's purchase or experience of movies in that if two different genres occur at the same time, the two might have some rules related.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">
 A. Maybe comparing the similarity between items can help with deciding meaningful, meaningless patterns. For example, with a high support and confidence between item also with a high similarity can justify the results, or reversely, if their similarity is low, that might be the more interesting pattern.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="15">
+      <c r="A15" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t xml:space="preserve">
 - transaction: E-commerce platform
@@ -2618,7 +2481,7 @@
 - An association rule: if someone purchases 'Baby foods', he/she will purchase 'Groceries' as well.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">
 - We can use top-k or top-p to reduce computation complexity.
@@ -2627,11 +2490,11 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+    <row r="16">
+      <c r="A16" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>An online shopping platform analyzes order history to find purchasing patterns.
 Transaction: A single customer's order, one complete purchase event.
@@ -2640,79 +2503,56 @@
 Suggest itemset: Netflix analyzes viewing history to find patterns in what users watch together.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>- Lift: measures if A and B are truly correlated, or just co-occurring by chance.
 - Conviction: measures how often the rule is wrong, how much it depends on B.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="17">
+      <c r="A17" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>In my experience there are many cases where pattern mining can be applied to, but the first thing that comes to mind is coupang. Based on recently seen or purchased items it suggests new items to the user. For example, a user buys {protein powder, creatine, eggs} or {banana, milk, eggs}.
 From this we can find that {protein powder, eggs} are the most frequent it can suggest {eggs, protein powder, resistance bands, energy drinks} when someone buys eggs according to the association rule. It can also suggest new items to a user. For example, suggest {resistance bands} or {energy drink} which in turn will increase associated things and profit sales and profit.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>pattern mining might be useful not only for human interactions but also creature interactions as well. for example, various "local ecosystem" can be transaction. Itemset could involve creatures of that local area. we could analyze which creatures tend to happen together. etc. this might be useful for biodiversity conservation.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>A supermarket analyzes millions of transactions to discover purchasing patterns.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Lift score</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>pattern mining example
 supermarket → transaction
@@ -2721,17 +2561,17 @@
    association rule</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>in addition, novelty can be an interesting pattern (is pattern new or already known?)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="21">
+      <c r="A21" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Best/Top
 - watching history
@@ -2742,7 +2582,7 @@
 Ex: Not bro is often watched with Moana</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Engagement
 Usually, when you watch video on YT "in most viewed parts" you can't see, based on that, predict future trends.
@@ -2750,11 +2590,11 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t xml:space="preserve">
 I think in aviation. That is a recent monitorings trends can be treated like a template, for example person A wants to discover europe countries, hence it will start from Paris → Italy → UK and others. It then if the airlines can discover the pattern, they could applied it into marketing strategy and sales strategy to gain the most of profits.
@@ -2766,71 +2606,52 @@
 base</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>The patient's medical record built of their symptoms. for example, anyone who got @ teen might (highly) cause it as well</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>• In addition of support or confidence, we can check the correlation whether the itemset has relation or not. So it can help to differentiate real relation rather than just a coincidence.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="24">
+      <c r="A24" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>I think pattern mining can be use in data mining
 For example, think of a game where we want to find unreleased contents, upcoming contents.
 We can have data from data mining file (file name date of creation, file type, related directory and so on. Let's focus on three itemset {file type, date of creation, related directory}. By finding on these items, we can come up with an association rule to determine content type → unrelease, in-use, upcoming which can satisfied our target.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>In addition to sup or conf, I think there are many "interesting pattern" but I am really not sure they are useful. For example, Noise → collect data cannot be always perfect, by looking at noise pattern, we can pinpoint origin of noise and eliminate them. Or we can use noise to determine whether the data is reliable, accurate and ready to use or not.
 Other interesting pattern could be determining a threshold point. For example, movie A 'box office' money is $10000. We can split the hair B = $7000 and C = $1000. We can say a lot of money by saying A is the most popular and make a lot of money than other two. But by determining a threshold of $5000, we can</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="25">
+      <c r="A25" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Real-world example where pattern mining can be applied :
 It can be applied to almost any real world problem to answer some question given a database. For example, today a pattern finds a similar that being a combination/set of transaction could be a list of "illnesses". An item set being which illnesses are found to come together and possibly come in causality, in those sheltered animals together. There are other examples, like going out loose depending in various frequent attributes, in hawking, Mental Skills, crimes committed, etc.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Aside from support and confidence, maybe there can be a frequent pattern of items never being together.
@@ -2838,11 +2659,11 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="26">
+      <c r="A26" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>KPOP merchandise selling.
 Item set: album, lightstick, photocard, keychain
@@ -2850,17 +2671,17 @@
 association rule: if A then B, if people buy album, usually they also buy photocard</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>i think maybe leverage like the coverage for large scale to find an interesting pattern, this so that the pattern will be useful for large scale use like business.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="27">
+      <c r="A27" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Online food delivery
 Transaction: {burger, fries, milks} → Order of one customer
@@ -2870,47 +2691,47 @@
 → If customers order a burger, they likely to order fries.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Correlation. correlation can be useful to determine whether items are truly related positively or negatively. This can avoid misleading patterns than occur simply because items are common.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="28">
+      <c r="A28" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Pattern mining can be applied to a streaming service like Netflix. In this case, a transaction can be one user's viewing history over a certain period of time. An itemset is a frequent itemset is a combination of contents that appears often a cross many users' viewing histories. For example, if many users watch both a crime drama and a detective movie, the combination can be considered a frequent itemset. An association rule could be {Crime Drama A} → {Detective Mark B}, meaning data users who watch Crime Drama A are also likely to watch Detective Movie B.</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Lift, because it shows whether two contents are related more strongly than expected by chance. Another useful criterion is unexpectedness, since a surprising pattern can be more interesting than an obvious one. Actuality is also important, because a portion is more valuable if it can actually help improve recommendations or user experience.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="29">
+      <c r="A29" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>→ I think pattern mining could also be applied to music streaming application. The transactions in this example would be playlists created by the user and items would be songs/artists. It can discover the listener's music taste through this method. The frequent itemset in this case would be as an example, through millions of pop music playlist, Rihanna and Ariana Grande was mostly found grouped together and appear atleast 17% margin (10K playlist).</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Consistency. If looking the example music above, does certain songs played over the same no. of times throughout the whole year or not. The answer can determine some pattern in listener's consistency.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="30">
+      <c r="A30" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t xml:space="preserve">
 → Personally, I think "MEDICAL DIAGNOSIS" is a (lipsh)
@@ -2920,7 +2741,7 @@
 Eg.: users who visit homepage → product page → reviews usually opted to checkout page.</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t xml:space="preserve">
 → Some researchers uses "leverage" such that
@@ -2936,56 +2757,11 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="31">
+      <c r="A31" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t xml:space="preserve">
 YouTube video recommendation
@@ -2993,34 +2769,30 @@
 From the UX perspective, it would also be helpful to society.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>food delivery apps. For example of the customer wanted to order fast food example for transaction is customer's frequent itemset.
 The itemset, {burger, fries, coke} &amp; frequent itemset is {burger, fries}. As people always order burger and fries as a set Association rule, people that usually order burger will also likely order fries. This is because it usually comes in set and the price will be lower than buying it as a la carte.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Check whether the pattern is consistent and trustworthy. Some pattern might look related but it might be appear by chance. Some pattern might look stark but actually random noise.
 For example during promotion it might show that burger may not be purchase together more with another dessert. This is not reliable as if only happen during promotion not all time.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="33">
+      <c r="A33" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Netflix recommendation.
 Transaction: { Avengers, Spiderman, Iron man }
@@ -3032,7 +2804,7 @@
 likely to obtain.</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Lift by measuring how much stronger the rule is than random chance.
 lift = (A→B)/(s(B))
@@ -3044,26 +2816,26 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="34">
+      <c r="A34" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>finding fraud transactions for banking system. The transaction can be the website, or terminal made the transaction. The transaction can be "website terminal time", a transaction is where a transaction is made such as {company, ip = z} and if suddenly there's a weird transaction or itemset appear with suspicious amount, that can be a candidate for fraud.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>History. We can learn about someone's behaviour through their history. same goes to finding "interesting pattern" in pattern mining. We can analyze the past history of transactions made to find the "more likely" pattern, as it can show a certain behaviour. If an item has a history of being purchased many times, it is most likely will be purchased again in the future.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="35">
+      <c r="A35" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Student course registration.
 Exp: Transaction = {DS, ML, AI, DL, CN}
@@ -3072,55 +2844,51 @@
 association rule = {AI} → {ML}</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Correlation. A part from that, frequent (costly value of information CVoI)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="36">
+      <c r="A36" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t xml:space="preserve">
 It is a restaurant, for example, Meal Plan B.
 The transaction is burrito, fries and soda. Itemset {a Burrito, fries}, {burrito, soda}. a frequent itemset could be {burrito, fries} as it is a popular item. Association rule is we can say that if a customer buy a burrito, then they will buy fries → {Burrito} → {fries}</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Relatability, a pattern need to be relatable for it to be functional, it could be inherently pattern but if it's not relatable to tools (in things) we are studying it could be coincidence</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="37">
+      <c r="A37" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t xml:space="preserve">
 I think that adidas Jimmer's selling data is applied to pattern-mining shoppers must be bought items they need. for example, like David, hank Burch, Many people are students living near. so, they buy writing equipment and household items intensity. Those characteristics could be shared by one Category. It makes will make a Jiao Increase the efficiency of sub-categories and a hike in sales. It must be very useful to create a new category specialized to subsets that are different from the existing categories.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>In youtube, I think one of example that pattern mining is applied to is Netflix/Youtube food videos recommendation. Transactions might be the genre of the movies such as {comedy, horror, romantic, fantasy ...}. Itemset might be the most and old genre. People who loves crime genre might be interested in horror, (mystery, ...) {horror, crime}.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>In addition to support and consistency, ∅∅ we should consider "how much MORE often X and Y occur together than expected" to strengthen the relationship together. If the leverage more to (positive) it might be interesting,
 (independent) and ∅ (negative) is maybe happen less than expected?.
@@ -3129,11 +2897,11 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="39">
+      <c r="A39" t="n">
         <v>48</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>I think market basket analysis can be a real world example. I learned this case in other class, so I can explain it well.
 A transaction is a customer's purchase, (ex. {milk, bread, juice}).
@@ -3142,7 +2910,7 @@
 Lastly, an association rule is a relationship like {milk → bread}, which means a customer who buys milk also tend to buy bread.</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Novelty
 If a pattern has support and Confidence (also lift), it's hard to consider it as an interesting pattern without novelty.
@@ -3150,17 +2918,17 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+    <row r="40">
+      <c r="A40" t="n">
         <v>49</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t xml:space="preserve">
 For telecom companies, they need to make promotions based on user needs. If correlation between two or more services are found, they can combine these services and market them. Also they may analyze leaving customers' patterns to prevent any loss of users.</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Distances between transactions may be helpful to find interesting patterns. Even if confident association rules are not found in the whole table, if clustered by distances (cosine, ucld, etc.) there may be strong association rules inside those clusters.
@@ -3168,31 +2936,12 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+    <row r="41">
+      <c r="A41" t="n">
         <v>51</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Beyond Support and Confidence, Lift is another key metric for analyzing patterns.
 Lift(A⟹B)= Support(B) / Confidence(A⟹B)
@@ -3203,57 +2952,57 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+    <row r="42">
+      <c r="A42" t="n">
         <v>53</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>I think pattern mining in real life can be represented by how a supermarket manages their product stock. For example, checking their market built selling each item method. so that they can use the associate rule to know which items related to each other and then put those item near to each other so customer can easily access them.</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>In my opinion other criteria that helps to find pattern is like special season or festival. In my case, in Malaysia during festive person the buying transaction of food products increase, especially food ingredient to make traditional food. In korea, maybe like buy buy people the buying of tteok increase during their public holiday. Sorry IM mistaken, other examples: pepero day, valentine, white day.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="43">
+      <c r="A43" t="n">
         <v>54</v>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Analyzing user's search keyword can be done by pattern matching. Since user's interest tends to search relevant keywords, We can identify the relationships between keywords. Using this, we can help recommendation algorithm and provide users to interesting in-service contents (etc. tagging) sometimes they see relevant and can recommend 'JavaScript' to 'Java function' then we can (automatically suggest related learning paths or documentation to guide the user toward their goal.)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>When we use both the words and respect the goal as their using, we can find all groups in Notion. Then if we can consider their distance and cluster them to dad standard groups, we can provide more concrete analysis.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="44">
+      <c r="A44" t="n">
         <v>55</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>A real world scenario where data mining can be applied to is with Netflix and the user's watch history. The user history to find patterns. Then a item set, we will catch a certain series. Thus.itern could be the user's watch history in a certain number of days as {군대들이, 어쩌피르, 가차 워이, etc.} Frequent itemset would be the combination of series that many people watch as {군대들이} → {군대마다 2} if the use is watch Squid Game 1.
 Association Rule in this case might be {군대마다 1} → {군대마다 2} if the user is watch Squid Game 1.</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Maybe trying to find unexpected situations could be another criteria to find unexpected things. Like big disused in class, disuse and less luxury bag personally unexpected, and this lead to an "interesting pattern" so it could also be a criteria to find unexpected of in the data and relationship can also be a criteria to find "interesting pattern" from data.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="45">
+      <c r="A45" t="n">
         <v>56</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>I think a real world scenario is when deciding the next combination of game genre. It (transaction).
 Transaction: a single instance of game of either each/used target
@@ -3268,32 +3017,13 @@
 In this case 6 (rougelike → decision making) &gt; 70%.</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>58</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>I'm interested in games. So I can apply pattern mining to Steam, a game distribution platform.
 transaction (Steam wishlist)
@@ -3310,24 +3040,24 @@
 We can see if someone has eternity in their wish list, they are likely to also have rule of rain in their wish list. It's association rule.</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Things users' gender and age group can also be other for finding interesting patterns.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
+    <row r="47">
+      <c r="A47" t="n">
         <v>59</v>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>A real world scenario when pattern mining applied to.
 The transferring system could be applied to a pattern mining. Targeting a specific bus or a station + subway system has massive data enough to satisfy some methods. By figuring the patterns out, we can find some demands on specific public transportation to lengthen or extra short cut to (citizen) is needed below.
 +extra explanation</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>What can be other criteria to find "interesting pattern"
 We may conduct a Medball ratio test on each events, where Hi: each events are independent. Because I think the "Interestingly" means something unexpected. By Conducting this test about the Jim Hi above and Ho being rejected. We can find unexpected relation that can more some profit
@@ -3340,11 +3070,11 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
+    <row r="48">
+      <c r="A48" t="n">
         <v>60</v>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>A real-world scenario where pattern mining can be applied to. (Possible Example)
 Transaction: Search Engines in Social Medias / Applications
@@ -3358,56 +3088,37 @@
 Without knowing what the items exactly are referred to.</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>61</v>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Sales → If a business sells a lot of goods but less sales for every type of goods are different, may might want to use pattern mining to see which goods to increase or decrease production.
 This can help save a lot of budget too.
 → Some Tech components like Apple usually have a discounts for students in which if you buy a Macbook, you will get an Airpod or have a fixed price. I want it takes pattern mining to see what parts items do students usually purchase together before deciding the offer efficiently.</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Type of data → when buying products, customers tend to buy products that they need for a specific goal. Let's say a customer's goal is to bake a cake, it they are purchasing flour, they might also purchase baking soda, brown sugar, vanilla essence etc.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="50">
+      <c r="A50" t="n">
         <v>62</v>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>the selling of goods at a department store. During sale time, store can analyze transactions made by customers. an itemset would be the item that they bought, such as milk. A frequent itemset can be an item that is frequently bought by all customers during that timeframe such as strawberries during its harvest season. An example of association rule is that many customers who buy stamps also bought conditioner. This suggests a strong relationship between these products and people tend to buy them together.</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Other criteria to find interesting pattern is leverage. This measures the difference between observed and expected co-occurrences, which focuses on actual impact and not just rotter. Two rules can have the same lift, but one affects way more transactions which causes it to be more useful.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
         </is>
       </c>
     </row>
@@ -3422,98 +3133,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Pattern mining finds rules that decide common structure and clustering sorts how groups of similar data. The similarities of the two concept and they try to find interesting features/structure from a large dataset. They make complicated data to be understood much more.
 The difference between the two would be that pattern mining tries to find relationship between the attributes which means clustering puts the entire object into groups.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Some other approaches for clustering could be by making it simple and only using features to cluster. For example, we could find the most significant/important feature from the data and we get higher (clustering) clusters those data into desired buckets. This might not be the best clustering objects, but for sparse data/objects this may be an option for useful, but for dense it could be mapping the high-dimensional data to a low-dimensional clustering. Mainly, often the lower dimension and the cluster hyperplane there is fewer dimension. This could be used to do clustering hyper-dimensional data.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Pattern mining and clustering appear to be similar in that they both involve going through data. The fact that they both find and use patterns in data is why. The difference is that a "pattern" is closer to finding information by using the frequency of data that appears often, whereas clustering is closer to looking at what is similar. Aside from that, it is good to consider that the two have similar meanings.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>If I were to think of another method, it would be to go by category. In other words, it is better to divide the fields and compare the data.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>What are conceptual similarities and differences between "pattern mining" and "clustering"?
 → Pattern mining and clustering are similar in some points. First, both are the ways of discovering information in given data. Also, there are many standards to do these methods. However, pattern mining is a kind of finding relations/rules like x→y, while clustering is a grouping of data with similar properties.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>I think we can apply "timeline" methods for clustering some data when the data is continuous against time. For example, some words appear only in particular moments, and we may utilize this point for clustering. Using random, KIDST data, and differentiated vibe1 clustering. (Example)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Pattern mining and clustering are similar in that they find statistical characteristics such as patterns and clusters in data. The difference is that cluster data clustering groups similar data based on factors like distance and density.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>All concepts are grid-based models: distance, density, and probabilistic. Even if there is a correct answer, similar clusters can be grouped based on occurrences.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Similarity: Both Pattern mining and clustering are methods for discovering useful structure from data rather than simply memorizing label. In other words, both are exploratory data analysis tools that help us understand what is hidden in dataset.
 ↳
@@ -3523,7 +3229,7 @@
 Also, there can be semi-supervised, ensemble-based, and validation-based clustering.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>According to lecture, I think clustering can be categorized by other approaches such as high-dimensional or scalable clustering methods.
 For example, high dimensional clustering is useful when the data has many features. (</t>
@@ -3531,17 +3237,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Similarities between pattern mining and clustering
 Both identify the scale (individual flow) of data.
 In addition, there are similar parts that both do well; pattern mining can find things, and clustering can also group things in a similar way.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>However, the meaning of clustering narrows the gap even down to the points that classify the space of the dataset. Clustering allows us to group data that we know, even within these groupings.
 Like the above,
@@ -3552,17 +3258,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Conceptual similarities &amp; differences between pattern mining &amp; clustering.
 Both topics try to find relationships between data, as in how the data might be correlated with each other.
 But clustering involves unknown ground truth between data, as in trying to find a relationship between data, despite not knowing exact information about some data.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Different approaches in clustering:
 Introduce a single parameter or a category to the data, then see how the data is exploited in a graph.
@@ -3572,30 +3278,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>I think they are similar in that they both analyze patterns in data to find meaningful results. Well, they are used to determine what the distribution of general data such as music, forms, and animals is like, and where the utilization models are applicable. Both can be seen as similar in that they are classified under data mining.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>I thought about a method to group data within a certain time frame by applying distance, density, and probability. I have become curious about how consistent the general distance and density methods are when used in conjunction with grouping patterns within a certain time frame.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Pattern mining is powerful in that, as the literal meaning of the word suggests, it can find trends embedded in the data. For interpretation, clustering determines whether data, such as which new music tracks are trending or data that is applied all at once, is different by examining the underlying foundations of data that have certain steps or stages.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>It seems that regarding the subjective nature of data, such as in games, activities where the outcomes or intensity have been prolonged are significant. It seems that activities where people enjoy the gameplay for a long time, or where the "life span" of the game survives, are classified as activities that persist.
 That is my thought.</t>
@@ -3603,10 +3309,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>conceptual similarities of "pattern mining" and "clustering"
 - both are collected from frequent patterns or structure
@@ -3623,17 +3329,17 @@
 - clustering → objects together</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>I am thinking on combining two approaches: distance and density on two different background but using some test subjects. For instance, we can use one person as a subject. we then divide his background into two different background: working background and life background; varying background and life background with big sets of data which by number of subjects we have two big sets of data which we apply two diff method. We then correlates both sets to find way you can cluster data across sets of data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Similarity - unsupervised learning
 • no labels
@@ -3643,7 +3349,7 @@
 Clustering focuses on grouping similar data points together.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Other clustering approaches:
 • hierarchical clustering
@@ -3654,10 +3360,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Pattern Mining | Clustering | Sim: both are not labeled data.
 Rules, dense, patterns | Data points in clusters | both want to discover
@@ -3665,22 +3371,22 @@
 Aim to find freq, parts | Aim to group data</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Hierarchical clustering. Like a tree of clusters.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Pattern mining and clustering are conceptually similar because both aim to discover hidden structures in undealed data. They are both useful for exploring data analysts and help us better understand the underlying patterns in a dataset. However, they focus on different types of structure. Pattern mining tries to find frequently co-occurring items or itemsets, they often use as different types of clustering, this is they works pattern mining focuses on grouping data and/or data points into clusters. In other words, pattern mining focuses more on similarities among features (or relationships among items or features), whereas clustering focuses more on similarities among items themselves.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>One is graph-based clustering, which models data as a graph and identifies clusters based on the connections between nodes.
 This is useful when the relationships among data points are more important than their physical distance.
@@ -3689,10 +3395,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Similarities -
 - Both are unsupervised learning methods
@@ -3702,7 +3408,7 @@
 - Pattern mining: 1) Finds frequent patterns, itemsets or rules</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Focus is on relationships between items
 - Clustering: 1) Groups data into clusters based on similarity
@@ -3715,34 +3421,34 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">pattern mining finds interesting patterns or relationship in the data, (answer pattern). clustering group similar data points together data, (answer group).
 both, look for pattern or interestingness.
 </t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Maybe use a graph like point or node in the graph is a data point and the edges between point is the relationship which is the similarity.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>By conceptual pattern mining finds pattern by looking on the frequency of co-occurring items and its output related on Association rule.
 Clustering's goal is to group object and one similar or related to one and another in same group together. We can expect on object from clustering in the first 4 sets of group.
 The similarities of these two approaches are uncovering and discovering often the labeled DATA is unsorted or unknown, we can leverage method when no labeled data, as we will discover hidden datasets structure in than two approaches.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Other clustering approaches like hierarchical clustering where it builds a tree like hierarchy and visualized as a dendrogram.
 - Grid based clustering when it quantizes object space into finite number of cells. Then a grid structure. Clustering will occur on grid rather than the distance points directly.</t>
@@ -3750,10 +3456,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>1 What are conceptual similarities and differences between "pattern mining" and "clustering".
 - Similarities = both applied the same thing as finding interesting connection (relation) or association between set of data.
@@ -3761,17 +3467,17 @@
 2</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Maybe line clustering method, with this we can add more line into the data so that we can see a good sign of cluster.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Between pattern mining and clustering both have to gather specifically, pattern mining can look for more interesting in finding things like rules in a group
 Similarities → pattern is related
@@ -3783,40 +3489,40 @@
 properties of self data</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>I would suggest pattern. Maybe that we sort from pattern mining could be used to cluster things together that we can group, in chapter, we begin them shows data assigns its cluster. So check that we what are within the same group/and that are another. Make later within the same group/data unless within the type two patterns might be used as pattern doing to try we got two patterns.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>In pattern mining, we try to find similar features of data object so that we can do meaningful analysis.
 In clustering we try to find clusters that can generalize the data points into a few group or noise.
 Conceptually in this two scenario, the similarities are that we are trying to see if these are data that are similar and happening frequently enough for us to draw conclusions.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Maybe we can use cosine similarity to find vectors that are actually similar but different magnitude.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>What are 4 conceptual similarities and differences between 'pattern mining' and 'clustering'?
 I think both processes have pattern that's need to be classified and make grouping data from a larger group to smaller ones. While the differences is pattern mining are derived from correlation and certain trend or repetition, clustering is more statistical say of grouping nearest data together and discard the relevant ones</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Can you think of any approaches for clustering, beyond 'distance',
 'density', or 'probabilistic' methods?
@@ -3828,10 +3534,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>→similarities and differences
 →pattern mining do preprocessed data, if that is corrupt etc or not compatible with the dataset to be used.
@@ -3846,7 +3552,7 @@
 → simple</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>other approaches:
 sequence / order of data within threshold. (20 entry per dataset).</t>
@@ -3854,32 +3560,32 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>pattern mining is the first step to learn some of the relationship of the relations. Meanwhile, clustering is a method to group some similar data points. Even-let-them are learn the pattern. one was partition one I group similar data together.
 For the similarities, both are trying to learn the data but just the output we got could be different.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Other approach, instead of learning, divide too calculations, maybe can use deep learning approach so that network will learn the representation before clustering, being some research, there one is deep Embedded Clustering (DEC).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>The conceptual similarities between "pattern mining" and "clustering" is both aim to find hidden structure when are pattern mining → relationship and clustering →groups. Both also can be unsupervised learning which is no rules and organizes pattern from raw data.
 Meanwhile, the differences these two are "pattern mining" find patterns and "clustering" find groups with similar data. The deep types of "pattern mining" is to discover data and clustering is to find common pattern. The output for pattern mining is rules for "clusters" is my data (numeric, text, etc). The output for pattern mining is rules and "clustering" is clusters.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Other approaches for clustering, beyond "distance", "density" or "probabilistic" methods.
 • maybe grid-based clustering, which it can divide space into grid cell, then cluster is may be grid-based. Secondly, graph-based clustering which represent data as graph and then cluster based on connections /relationships.</t>
@@ -3887,41 +3593,41 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Pattern mining is based on frequent pattern and relationship if it is to find what they its occur together. meanwhile cluster is just cluster similar group of similar data point in to cluster. It is to find similar pattern mining which data point is similar. The similarities is both pattern mining and clustering is unsupervised data mining technique. Because there is no label data. Both is also used to find pattern, which is to find group, pattern mining used to find typical pattern and cluster is to find them relationship. The difference is pattern mining is used to find them relationship meanwhile clustering is for object similarity.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Constraint based clustering: Cluster it by satisfying user defined constraint or rule. Consider additional condition give by user or application.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>The conceptual similarity between pattern mining and 'clustering' is that the result of (mathematical) operations may not be always interesting, because of the chance of noise hidden in the dataset.
 And the difference is that pattern mining discovers 'patterns' which are 'frequent' items, subsequences, or substructures, whereas clustering nears similar or 'close enough' data points into clusters.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>In case of clustering Social network. data such as X (former Twitter) follower network, I would insist on using 'following' information as a connectivity - base similarity measure. Since traditional approaches seem to be problematic to be defined in this context.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>What are conceptual similarities and differences between
 "Pattern Mining" and "clustering"
@@ -3932,7 +3638,7 @@
 (or converted data form different type if is homogeneous).</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>I think there is no such method. Because any methods that we use are mostly transforming data, extracting features, and convert them into numeric data. At the end,
 We choose one of "distance", "density" or "probability"
@@ -3941,31 +3647,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Clustering and pattern mining are both unsupervised techniques used to discover hidden structures in data. Clustering involves grouping objects into clusters, while pattern mining finds frequent patterns or association rules in data. Thus, clustering focuses on grouping, whereas pattern mining focuses on discovering relationships.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Yes, there are other clustering approaches beyond "distance-", "density-", or "probabilistic" methods. For example, hierarchical clustering builds a tree-like structure, and grid-based clustering partitions and data space into grids. Additionally, model-based and constraint-based clustering can incorporate prior knowledge or rules into the clustering process.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>They both find data's common contents/similarity. They both are unsupervised learning.
 However, clustering focuses on shapes, but pattern mining contrasts on finding correlation/cause and effect.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Clustering can be similar with classifying if there are low number of clusters. Will clustering with labels helpful?
 Also, like network of networks, we can make cluster of clusters.
@@ -3975,42 +3681,42 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Both pattern mining and clustering are unsupervised methods that discover hidden structures in data, but while pattern mining focuses on identifying frequent co-occurrence relationships among items, clustering aims to group data points based on their similarity.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>I think there is a way to distinguish groups by defining specific ranges.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>The commonality between Pattern Mining and Clustering is that they can discover certain features within data. I believe this is also true in the sense that data is grouped into similar sets.
 The difference, I think, is that while Clustering simplifies things into simple individual units, Pattern Mining focuses on what lies deep within the data itself.
 Clustering learns by bringing those things into the data.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>I think that having too many clusters might result in overly granular analysis, making clustering ineffective.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>similarities
 unsupervised learning: They do not require labeled data and aim to discover hidden structures or relationships within the data.
@@ -4024,7 +3730,7 @@
      patterns</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Grid based clustering: divides the data space into a finite number of grids and performs clustering on the grid structure.
 Constraint based: Incorporates user specified constraints into the clustering process.
@@ -4033,17 +3739,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Both of two make groups from the datapoints.
 While pattern mining make groups based on how frequently they occur together,
 clustering make groups based on how similar or close they are.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>we can first classify the dataset on labeled criteria,
 and then, cluster the points that are on similar location in each group.</t>
@@ -4051,10 +3757,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Similarity: 'pattern mining' and 'clustering' find kind of pattern in given data set Difference: 'pattern mining' can find not only clusters, but also other patterns like trends (include) or relations.
@@ -4062,17 +3768,13 @@
 "If-then" rules. I think it is very inefficient, but it can be used when data set is small and we need very accurate clustering result. Additionally, we have to know largely how clusters look like in advance.</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Pattern Mining and clustering are to find hiding structure in data.
 data learning is only data without (label and based on similarities).
@@ -4081,24 +3783,24 @@
 Clustering's output is cluster, pattern mining's output is frequent itemset.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>I think using graph. Keep its similarity is other approach for clustering.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Similarities and Differences between Pattern Mining and Clustering
 Similarities: Both form data clusters (finding groups) and identify meaning. Both observe data based on similarity or character-based concepts.
 Differences: Clustering is based on similarity, whereas pattern mining also finds synchronous patterns (finding words). The meaning lies in the "speed" (frequency) of the data. The "speed" (frequency) points and stages of the data are what define them.</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Besides distance, density, and probability, other clustering methods can be explored by examining what exists after clustering the data, and then proceeding with the data.
 =&gt; "It seems that there are parts that share the same characteristics.
@@ -4107,15 +3809,15 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>The most similar aspect of pattern mining and clustering is that both are used to find certain patterns in usage. While the two methods are similar in how they help, they differ somewhat in terms of whether or not there are stages. Therefore, even if they have other similar data, they both aim to find meaning, but they have different implications. Pattern mining is meaningful in finding change patterns in data points as they move through different stages or dimensions, whereas clustering is more meaningful in how it distinguishes things as separate, even when they seem similar to other things.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Creating such clusters differs in dimension; however, creating different clusters for each node, and the stages involved, creates a difference, and therefore, the data is staged accordingly.
 Analogies use clustering.</t>
@@ -4123,16 +3825,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Pattern mining uses "support" and "trust" value to measure, while clustering basically uses distance and density.
 However, they are similar to finding some useful data by organizing what to like similar between objects.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>I think if data can be clustered by inner product
 of cosine, which means "they have same directions". I think same direction can provide the ratio of data occurrence. So they can be clustered.
@@ -4144,42 +3846,42 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Pattern mining and clustering are both unsupervised learning to discover interesting ideas, without relying on labeled examples.
 Pattern mining focuses on discovering recurring relationships among items (e.g., co-occurrences, sets..). Clustering aims to partition data points into groups using spatial information on the fly.</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>I think clustering by encoding can be on another approach. By using neural network (e.g., autoencoder), with some known metrics (e.g., contrastive losing), it can be partitioned with details (e.g., BIST/it is) value computationally heavy. I think technique should be seriously considered before application.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Similarities: Both retrieve information to process data. As a criterion, clustering uses distance, while pattern mining uses frequency, count, etc. Their methods are similar, but their criteria differ.
 Differences: Clustering creates groups among close data and recognizes different data as separate.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>NOISY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>What are conceptual similarities and differences between pattern mining and clustering?
 Similarities: Both are to find things in common in a set of data.
@@ -4187,34 +3889,34 @@
 pattern mining has its setup and impact whereas clustering uses distance matrix.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>I guess there is k-means which is centroid based and hierarchical which is connectivity-based.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Conceptual similarities and differences between "pattern mining" and "clustering"
 Clustering involves grouping objects that are similar to one another to one another while pattern mining involves discovering substructures that occur frequently together in a dataset.
 They are similar in a sense that both processes aim to get underlying structures within the dataset and summarize the data to make it easier to interpret.</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>graph-based clustering</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>What are conceptual similarities and differences between "pattern mining" and "clustering"?
 Pattern mining focuses on discovering rules among items in dataset, such as identifying items often bought together.
@@ -4222,7 +3924,7 @@
 Both are unsupervised learning but pattern mining looks for specific relations while clustering looks for similar objects.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>As we learned today, we can think of hierarchical clustering.
 As another approach, we can think of graph-based clustering.
@@ -4231,16 +3933,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>They are both used to organize data set and extract information that we can get from the data set.
 Pattern Mining is used to find frequent patterns among the data, while Clustering is used to group similar data together.</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Both do not have 'correct output' or 'correct structure' because we use them to find unseen structure from an existing data.
 Pattern mining can overlap and similarities and differences of one point in case on are clusters.
@@ -4250,10 +3952,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>• Similarities:
 Both of them are unsupervised learning which we discover the structure or patterns of data without ground truth.
@@ -4262,47 +3964,47 @@
 clustering is collecting data points and grouping them based on certain rules.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>One of the other approaches might be grid-based method. The data points on the graph are observed and grouped based on the grid positions in the graph.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>The similarities between "pattern mining" and "clustering" are they both observe the data and explore hidden information that help in decision making finds the data. The different is that "pattern mining" finds relationship between data and output rules or pattern, while "clustering" groups similar data and form cluster.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Beyond "distance-", "density-" and "probabilistic-" methods, clustering may use graph where node as data point and edge as relationship. The outcome may be visually appear.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Both pattern mining and clustering are unsupervised techniques used to discover structure in data, but they focus on different types of insights. Pattern mining aims to find frequent or associated itemsets, like "items bought together," while clustering is to find natural groupings of data based on similarity, putting like things in same cluster. Both share the goal of revealing hidden patterns without labels, but pattern mining looks for specific item-level relationships, whereas clustering focuses on the overall structure of the data.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Beyond the mentioned methods, another important approach is graph-based clustering, where data points are treated as nodes in a graph and clusters are formed based on connectivity. Additionally, indirect methods like deep self-supervised clustering are useful, when data lacks clear definitions efficiently which can be useful. Methods like spectral clustering can be useful, but als by structure or connectivity, or technical requirements.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Pattern Mining ↔ Clustering
 Similarity: They have in common that they analyze data (knowledge, information). The definitions related to Pattern Mining are perceived as a Co-Concept, and similarly, Clustering also forms classes of data in this relationship as they go through their own stages.
@@ -4310,24 +4012,24 @@
 That is the result experienced.</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>NOISY</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>What are conceptual similarities and differences between
 Pattern mining and clustering.
 They find interesting information by collecting patterns. The patterns may be also some kind of similarity. Difference can be that clustering is more a grouping method for datapoints and pattern mining is a method for interpreting relations between data.</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Can you think of any other approaches to clustering, beyond distance/density probabilistic?
 A: Maybe for certain specific datasets, pre-defined bounds or lines can work as clustering in case of classification.
@@ -4337,17 +4039,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Similarities: Both are unsupervised approaches that discover structure in data without labeled examples. Neither requires predefined answers.
 Differences: Clustering partitions data points into groups such that similar instances are assigned together.
 Pattern mining finds relationships among items or attributes, like frequent co-occurrences, sequences, or association rules.</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Graph Spectral - based: Data is treated as a graph. clusters are found via eigenvectors of the graph Laplacian. The criterion is topological connectivity, not raw distance.
 → non-convex, irregular-shaped clusters are handled well.</t>
@@ -4355,16 +4057,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>• The conceptual similarity between pattern mining and clustering is that we want to find some interesting features between datas that are collected by using the similarity between datas.
 The difference is that in pattern mining we use the frequency of the data. and in clustering we use the distance or the probability of the data.</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>• We can use the notion of harmony for clustering.
 For instance, we can cluster numbers that are illustrated in (ratios?) by multiples in ratio of natural numbers. In the science of harmony, there are 12 keys in the piano. Each keys are clustered (most pitches) number.
@@ -4374,16 +4076,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>What are conceptual similarities and differences between "pattern mining" and "clustering".
 Pattern mining and clustering both looks for repeated and similar data points. For instance, pattern mining discovers rules of patterns shopping lists by finding frequent items and Clustering groups similar data points together. However, they differ in how they are affected by scale. Clustering is more complex than pattern mining as it is affected by representation. If feature set is changed, the different clusters are generated.</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Other approaches for clustering
 For if we discretize all the features that represent data points, we may construct a decision tree. From the root of the tree, if we apply division with a feature that reduces entropy the most, we may obtain leafs that represent clusters.</t>
@@ -4391,10 +4093,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Conceptual and difference between "pattern mining" and "clustering"
 I think the main concept is about finding interesting and useful patterns for both methods. And one of the main different
@@ -4402,32 +4104,13 @@
 "clust" on the other hand, try to group not similar data in a similar group. It does not normally remove from original set of data but it try to group every data in every possible way. Ofc, as a side effect, some data might come out as noise, not belonging to any cluster. I would not call this pruning but a form of natural selection that just happened along the way. not actively searching for noise.</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A54" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Conceptually they're similar in a sense that both perform mining and clustering are used to find useful information when needing that data to be labeled.
 I think the difference lies in the fact that they have different methods when finding data relevant useful data.
@@ -4435,94 +4118,60 @@
 Both are useful, of course, but what kind of right differ depending on what we aim to discover from the data we give find data.</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>The concepts of pattern mining and clustering are highly significant in data analysis.
 Both can uncover insights between data; one can discover patterns to compare similar data in clustering, and one can identify association rules from clustering. Therefore, both are similar stages of thinking in terms of handling data to transform and compare data by identifying patterns in these fields.</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>NOISY</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="56">
+      <c r="A56" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>They both try to what condition of feature has direct to mean.
 basically each data by sorting and slice the interaction to your algorithm with a recomputation. However, having always to cluster, I think the distance of them is that pattern mining (might or in the modern test (A and B has solutions because if (...) and clustering would on the group itself (Forgot there data by use the theory ...) So I think they are not mutually exclusive method.</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>We can divide the feature space by gives or informed criteria. like dictate this method will have closer similarity in the result.</t>
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>58</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pattern mining and clustering are both unsupervised learning methods that aim to discover hidden structures in data. However, pattern mining focuses on finding frequent or meaningful patterns, while clustering groups similar data points into clusters based on similarity or distance.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes, other approaches include graph-based clustering where data points are treated as nodes and clusters are formed based on connectivity, and model-based or deep learning approaches such as auto encoder-based clustering.</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Pattern mining and clustering are both unsupervised learning methods that aim to discover hidden structures in data. However, pattern mining focuses on finding frequent or meaningful patterns, while clustering groups similar data points into clusters based on similarity or distance.</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Yes, other approaches include graph-based clustering where data points are treated as nodes and clusters are formed based on connectivity, and model-based or deep learning approaches such as auto encoder-based clustering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A58" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Similarities: Both are unsupervised
 Differences: Goals are different.
@@ -4531,7 +4180,7 @@
 but "clustering"'s goal is to group</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Graph-based approach can be one of approaches.
 We can think about Graph
@@ -4539,42 +4188,42 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="59">
+      <c r="A59" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Both pattern mining and clustering is a method use to find hidden structures in data, that's the similarities. The difference is clustering focus on the rows of object, try to bucket group every data point into buckets of same item. Pattern mining search for specific combinations or items that frequently occur together.</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Maybe we can use grid, turn the whole data space into giant sheet of graph paper, computer can look at the grid and make analysis, like which cell are full and merges them together.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="60">
+      <c r="A60" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Pattern mining and clustering are both ways to separate data into several partitions and labeling them. Pattern mining finds frequent patterns from massive datasets and clustering partitions data points into groups. Both of them collects close with similar features together.
 Difference is that pattern mining focuses on finding recurring sequences, or co-occurrence chains between data while clustering focuses on grouping data objects that has similar features.</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Other approaches include high-dimensional clustering and scalable Clustering. Also we can think visual-insight-based, semi-supervised clustering.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+    <row r="61">
+      <c r="A61" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Conceptual similarities and differences between pattern mining and clustering?
 Similarities
@@ -4590,54 +4239,54 @@
 appear together freq.           similar to each other</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Any other approaches other than 'distance based' and 'probability methods
 → Grid-based method (Divide data with finite no. of cells (g DBR)                            → Self-organizing Maps (SOM) (use neural networks for clustering) ↳ use of map processing and map visualization</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+    <row r="62">
+      <c r="A62" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Similarities: Both are identical in that they find patterns that can be discovered in data.
 Differences: Pattern mining - utilizes relationships between data; Clustering - groups similar data into one unit.</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>NOISY</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+    <row r="63">
+      <c r="A63" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Similarity: Both methods are identical in that they find meaningful structures within data, and they are similar in that they analyze data quantitatively.</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>NOISY</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+    <row r="64">
+      <c r="A64" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Both pattern mining and clustering revolves around unlabeled data to find 'interesting' pattern and relation between each other. However, pattern mining focuses on the association rule or frequent pattern while clustering focuses on the partitioning and grouping of the data.</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Maybe using grid? Make a grid on the datasets and clustering is performed at the level of the cells rather than individual data points. So, instead of comparing the pairwise distance, just look at the spatial arrangement.</t>
         </is>
@@ -4654,139 +4303,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Example of outlier detection is there is someone login our account in another device that we not owned. A student answer quiz that has lot of question correctly in very small amount of time.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>I think AI agent can identifies outliers just effectively as statistical or distance-based approaches because it is trained by this same method. The advantage it has is identifie which method is best for each case.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>A. I think AI Agents are better at written detection. As we learned today, defining a data as outlier is too much context-sensitive. Sometimes the data can be a noise point a unstable point on the century while we can investigate the outlier using statistical or distance based approaches they aren't aware of external contexts. For instance, what if the data regarding human height was abnormal externally such as all kept have around 10 meters of height? LLM has what external context easily detect, easily 'awareness gaps' while other approaches won't.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>1) finding someone that scores much higher than other student
 using images of the same object to learn outlier detection to detect anomaly (maybe pipe?)
-More effectively, even better than human.
-reason 1: It can also see the data points as image input like human do, which can be faster with large no. of data points.
-reason 2: Most distance-based algo require us to tune the parameter which can require humans intervention. The AI can do this by itself and improve when needed.   TYPO
 자율주행차 detecting a pothole on the road and avoid it
 To find the best restaurant in Anam!</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>More effectively, even better than human.
+reason 1: It can also see the data points as image input like human do, which can be faster with large no. of data points.
+reason 2: Most distance-based algo require us to tune the parameter which can require humans intervention. The AI can do this by itself and improve when needed.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>I think AI agent that identifies outliers more effectively? Maybe both are using similar formula or algorithm, or even the same one, but the computation ability of AI agent may be faster thus more effectively. Besides, AI agent may do classification better therefore provide various accurate versions.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>In my opinion, nowadays AI agents can work more effectively in detecting outliers in most of the general cases. If the prompts are given clearly by users the AI agents can work well, therefore computational cost and time are saved. But since it cannot guarantee the accuracy in real world cases we still need those statistical/distance-based approaches to improve in the process of outlier detection.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>It seems that AI could be used to identify new species based on their characteristics. For example, humans are classified as having two legs and two arms, but it would be difficult to classify a newly discovered alien species using that existing framework. In such a case, if we show the AI a photo of the alien and define it as having six legs and four arms, the AI could use that data to determine that it is a new species. This would allow for more effective species classification and the ability to handle new data, such as that of an alien species.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">healthcare/diagnosis - abnormal heartrate, blood pressure or lab results can be outliers
 Online shopping - a user suddenly placing hundreds of orders in minutes could be also
 </t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>AI agent can be more effective but not always
 AI agent
@@ -4804,10 +4431,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Real world examples of outlier detections.
 - Network Intrusion Detection
@@ -4819,37 +4446,29 @@
   → Contextual outlier (the sentence is odd given the situation).</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>it depends heavily on what data type and task. One common example is, AI → 2200 shot defection ⇒ Can flag anomalies on aero training data on what 'normal' looks like. Methods → No hallucination risk ⇒ AI can confidently identify something as outlier even often it's not. Statistical/proximity methods don't have this.Apart from that, the computational cost for these methods are commonly higher than using AI, since AI used already a pretrained model or they can apply various method (knowledge distillation/transfer learning).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
         <is>
           <t>In my opinion if the data is a numerical data it is better to use the statistical distance based approaches but if it is for surveillance or image outlier it is better to use AI agent. This is because there are a lot of AI models that has already pre-trained for image detection and there AI agent actually make use of distance based approach to get the loss while detecting the image. Thus, it depends on what data are we searching outliers from and the effectiveness can defer.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>In my opinion, I think AI agent can be more effective in detecting outliers than traditional method if the dataset is complex and heavy. Statistical or distance-based approaches may be best in computation if the data is small, but may not be as effective as AI agent in detecting outliers.
 Many real world examples involves high-dimensional data that relate so many categories and label within a single data.
@@ -4858,45 +4477,41 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">Real world examples of outlier detection include fraud detection in banking transactions, identifying defective products in manufacturing, and detecting abnormal patient data in healthcare. </t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>AI agents and detecting complex, nonlinear patterns and context, making them often more effective than traditional statistical or distance-based methods in high-dimensional data. However, statistical approaches remain more interpretable and reliable in simpler settings with clear assumptions.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">Outlier detection appears in cybersecurity, e-commerce and sensor networks. </t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>AI agent can adapt over time and detect subtle anomalies, but they may overfit or produce false positives if data quality is poor. Distance-based and statistical methods are simpler and faster, making them more robust for real-time or small-scale applications.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>A clear answer is that AI seems to use outlier detection, and it has good and useful answers. Therefore, even if AI agents are more accurate, they are more “suitable/adaptive” in a practical way. In that sense, “even when the data is not very clear,” AI can still provide a detailed-looking explanation based on some evidence.
 However, to make the result better and more reliable, statistical methods should also be used at the same time.</t>
@@ -4904,31 +4519,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A. detecting unusual amount of money withdrawal from ATM - might be phishing victim</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">One outlier-detection example is detecting hackers in online games, such as too high shot-rate, impossible movement speed, or perfect accuracy.
 </t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>I think there are specific situation where AI agents detect outliers better than statistical methods. For example in case of hack programs in game, it can be easily detected by statistical methods because everything is measured by specific value (e.g. shot-rate, movement speed).
 But in case of normal text, such as text written by human and AI, AI cannot be measured by fixed statistics, so AI could detect better.</t>
@@ -4936,16 +4547,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">We can react to server disaster quickly by detecting weird metrics.
 </t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">
 LLM can't directly process manage by data. Context window is too small.</t>
@@ -4953,15 +4564,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>I think that an AI agent would identify outliers more effectively using the statistical method.
 Statistical methods rely on a predefined data distribution model which makes outliers more efficient.
@@ -4970,256 +4577,186 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A19" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">Real world example of outlier detection include credit card fraud detection, identifying defective products in manufacturing, and spotting unusual medical test results. </t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Traditional statistical or data-based methods are effective for structured numerical data and are easy to interpret. However, they may struggle with complex or unstructured data, such as image. AI agents like Claude can detect outliers in more complex scenarios by understanding context and patterns beyond simple statistics. For example, AI can spot awkwardly worded sentences in news article or unusual pattern in images.
 Likewise, AI methods require huge datasets and may lack transparency. So, AI agents can be more effective for complex data, while traditional methods are reliable for simpler, structured data.</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>In the financial sector, there is a secret to how AI agents can perform tasks like detecting outliers in credit card fraud (e.g., detecting transactions that are unnatural when compared to typical usage patterns).
+In the medical field as well, AI agents can perform tasks like detecting outliers in patient monitoring (e.g., heart rate analysis), making them potentially more effective due to the quality of the data produced.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-In the financial sector, there is a secret to how AI agents can perform tasks like detecting outliers in credit card fraud (e.g., detecting transactions that are unnatural when compared to typical usage patterns).
-In the medical field as well, AI agents can perform tasks like detecting outliers in patient monitoring (e.g., heart rate analysis), making them potentially more effective due to the quality of the data produced.</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="A21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>An AI agent can perform analysis through detection, and while methods such as statistical ones will have the most influence, outlier detection seems to be more effective.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>An AI agent can perform analysis through detection, and while methods such as statistical ones will have the most influence, outlier detection seems to be more effective.</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A22" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Credit card - If a payment occurs at a place not typically visited, it is considered an abnormal transaction.
-Exercise measurement - Aside from excessive exercise, it tracks patterns of usual physical activity. It is appropriate for monitoring anomalies like unusual heart rate or movement.
-AI Agents vs. Distance-based methods
+Exercise measurement - Aside from excessive exercise, it tracks patterns of usual physical activity. It is appropriate for monitoring anomalies like unusual heart rate or movement.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AI Agents vs. Distance-based methods
 AI agents are capable of detecting anomalies by measuring the distance of occurrences. They can also handle complex or latent operational distances.
 While distance-based methods might determine similarity based on proximity, they often lack the capability for real-time recognition or processing of the many complex, varied, or high-dimensional patterns encountered in real-world scenarios. They struggle to identify the diverse and rapid changes in behavioral patterns. Therefore, AI is being used to bridge this gap.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t xml:space="preserve">The score that exceeds 100 in test scores could be considered as an outlier.
 </t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>AI agents will identify the outliers better than statistical or distance-based approaches because they exploit more background knowledge about the data itself.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="24">
+      <c r="A24" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve">Outlier detection is used in fraud detection (unusual transactions), healthcare and manufacturing.
 </t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>AI agents can be more effective for complex of high dimensional data because they capture patterns and context, but statistical or distance-based methods are more stable and interpretable when data is simple and well-structured.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="25">
+      <c r="A25" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">Credit card companies use AI to flag a purchase made in a foreign country as an outlier, whereas manufacturing plants use sensor data to detect microscopic vibrations that signal engine failure.
 </t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Since AI agents can analyze hundreds of variables simultaneously, identifying hidden anomalies that simple statistical thresholds often overlook can be easier.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>NOISY</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="26">
+      <c r="A26" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t xml:space="preserve">Suppose I want to investigate the asset of Korea University students who graduated in 2010. There can be outliers who bought 10 bitcoin in 2010 and became rich because we should detect them because they can overestimate the average of the asset.
 </t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>I think AI agent can detect outliers more effectively. They understand the context of the situation and use it as the knowledge. For example, suppose that we are analyzing the sales of Pistachio annually. Traditional methods can regard "2026" data as outliers. AI agent has knowledge of Dubai cookie. so, they can regard it as normal data.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="27">
+      <c r="A27" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t xml:space="preserve">Outlier detection can be applied to stock market analyst, for instance. More specifically, [crossed out] a high volume buying/selling funds can indicate possible abnormalities. In future event, and traders can be more aware and prepared.
 </t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>AI agent can be more efficient in finding outliers in terms of versatility of data, and its contrast while statistical data outperform AI in terms of consistency and faster identification.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="28">
+      <c r="A28" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">the credit card fraud.
 In structured numerical problems, outlier detection can be used. Using pattern data like amount, place, and time, we can figure out suspicious activities (like two multiple transactions in 30m (Asian community)).
 </t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>An AI agent can be useful when the data structure is humans or semantic rather than just numbers. Like the example in the slide, determining outliers in the news article. (Pictures/or multimodal cars) should be handled with AI agents. However, it a task can be managed through numbers not heavily encoded with neural networks, it is unnecessary to use AI agent because of the computation cost and multivariance. (However, AI-generated code can be higher.)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="29">
+      <c r="A29" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Since outlier detection is a subtle task, it is a task that requires a more exemplary approach. Therefore, AI Agents will perform better by leveraging multi-modal capabilities. For this reason, verification activities for AI Agents have become a significant area of focus. In particular, it is about AI Agents effectively detecting outliers by leveraging context and knowledge.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>In certain complex situations, distance-based models work by performing subtle detection tasks, so distance-based models are a good choice for these types of tasks. When utilizing AI for these detection tasks, it is a good approach to leverage specific, task-oriented detection methods.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="30">
+      <c r="A30" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t xml:space="preserve">Real-world examples to find outliers.
 Scholarship process, where in this world everyone gets higher good grades. Surprising requirement, you do to scholarship championship/tournament but are the one with outstanding talent, capability always wins the chances. (Usually with scholar of acceptance rate is 4 1.75)% than the prom choose 2 students out of 10,000 participants.
 </t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>AI agent identifies outliers more/less effective than statistical/distance based.
 In terms of speed/performance, AI Agent effectively identifies outliers since they are multiple agent working to execute the plan of finding the outliers. However, since AI Agent have the possibility of hallucination and prone to make own decision making, hence statistical/distance → math/facts based model is more effective and trustable.   ← best
@@ -5227,11 +4764,11 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="31">
+      <c r="A31" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Think of real-world examples of outlier detection.
 Discuss whether an AI agent (e.g. Claude) identifies outliers more or less effectively than statistical or distance-based approaches.
@@ -5240,66 +4777,51 @@
 etc store</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>AI agent may detect outliers more effectively in the case of collective outliers because by statistical or distance-based approaches, outliers are determined by number of neighbours, and as collective outliers usually stick together/near each other, statistical or distance-based approach count may mistake it as inliers.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="32">
+      <c r="A32" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t xml:space="preserve">An example of outlier detection would be from data cleansing. We can use this outlier detection to distinguish random, or inappropriate error that we want to avoid. The phenomenon might generated by some different mechanism. For example, there is innovative error in two all expected data.
 </t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>AI agent could be more effect to detect outlier because statistical method might be limited if data does not actually fit the assumed distribution. Meanwhile distance-based can be computationally expensive due to some distance calculation.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="33">
+      <c r="A33" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t xml:space="preserve">Many examples are around us: Plagiarism detector, game cheating/bot detector, AI slop detector, etc...
 Where a category which needs security/honesty/integrity outlier detector can be used.
 </t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>It's up to AI agent's status. The more training data was given, the better result.
 However, there is always an attempt to bypass the detector, the model must be updated frequently.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="34">
+      <c r="A34" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t xml:space="preserve">Think of real-world examples of outlier detection.
 → I think outlier detection can use to make weapons.
@@ -5308,87 +4830,68 @@
 </t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>AI agents are based to train by are trained by statistical or distance-based approaches.
 Apart AI agents are written by [crossed out]. However, as AI agents are capable of using more diverse data to clearly and effectively perform detection tasks, they can handle outliers by applying more appropriate detection methods, thereby achieving a higher degree of accuracy in their detection processes.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="35">
+      <c r="A35" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
         <is>
           <t>I think it depends on the complexity of detect the data. For example for detecting outlier in the simple data like data entry error or typo in values. Statistical or distance-based approaches is more better, cheaper and reliable. But, for a complex data sets or pattern like fraudulent transaction, money scanning or advanced scamming. AI agent seems to be more effective even though it would need massive amount of data and money to be used.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="36">
+      <c r="A36" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t xml:space="preserve">Outliers can be view as both positive and negative things based on the perspective. Raising temperature can be view as a noise/error or indicating a global warming. This is not really a good subject to write since it is controversial and sensitive interaction. But I will just write it here. Since old ages, people have been doing outlier detection. For example, during the 80s, people burn abnormal people as witches since they are afraid and think of them as a cluster of outlier. Even more controversial one is that since pwa great great ... great ancestors, they will have a strange feeling when someone has different culture, skin tone, language and so on. These days, this term is called racism. In a way, racism is a form of real and sensitive information. People have been doing consciously and/or unconsciously. Think about it for a minute. Humanity has built in outlier detection and they can spot them easily.
 </t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>I might be wrong but I think at first, AI is good at distance-based since most of them are calculations.
 But now that AI has improve a lot and there are a lot of good truth labels to train, currently statistical based is getting better and better each day. Like AI might not be able to find Waldo but now I believe they can.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="37">
+      <c r="A37" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>A real world example of outlier detection can be found in daily health tracking data. For example, a smartwatch or phone app may [crossed out] record a person's number of steps each day. If someone usually walks around 8000 steps a day, but suddenly shows 7000 steps in one day, that value could be considered as an outlier.
 It may reflect an unusual event such as a long trip or exercise session, or it may also come from a recording error. This shows that outlier detection can be useful even in simple everyday situations.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>In my opinion, an AI agent such as Claude may be helpful for interpreting outliers and explaining why they seem unusual, especially when context is important. However, statistical or distance - based approaches are usually more effective for actually detecting outliers in a consistent and scalable way. These methods are clear numerical criteria, which makes them more reliable for large datasets. Therefore, I think AI agents are better used as supportive tools while statistical or distance based methods remain more suitable for core outlier-detection tasks.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="38">
+      <c r="A38" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t xml:space="preserve">The real world examples of outlier detection include credit card fraud detection (unusual transaction/unnormally high price), industrial inspection (defective items must be identified), etc. These examples show that outlier detection is important in many areas, especially finance, manufacturing (I think/it can be used in healthcare or security areas, but don't come up with some examples)  intrusively
 </t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>I think whether an AI agent could identify outliers more effectively than statistical or distance based depends on problem. In structural data with clear numerical behavior, statistical or distance-based methods are often more reliable.
 However, when the data are high-dimensional, unstructured, or heavily contextual,
@@ -5398,16 +4901,12 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="39">
+      <c r="A39" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
         <is>
           <t>When a stock's trading volume spikes 10 times in minutes, classical methods struggle.
 Statistical methods: rely on fixed historical averages but market commonly constantly shifts with earnings seasons and macro events → unreliable.
@@ -5418,16 +4917,12 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="40">
+      <c r="A40" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
         <is>
           <t>I think Agentic AI's can be identify outliers more efficiently than previous approaches with good enough prompting.
 I think AI can cover possible previous approaches.
@@ -5436,16 +4931,16 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+    <row r="41">
+      <c r="A41" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>If most payments are made only domestically, but a payment is suddenly made from overseas, credit card companies will treat this as an outlier and send a notification to the cardholder, and in the case of a large amount, they may even take measures such as suspending the card.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>When detecting things like spam mail, statistical or distance-based models can identify a large number of links, specific words, and patterns to determine if it is spam, but AI agents will be much better at uncovering hidden intentions or context. For basic data such as numerical data, existing methods may be better at detection than agents.</t>
         </is>
